--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -14619,10 +14619,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772906</v>
+        <v>118772912</v>
       </c>
       <c r="B123" t="n">
-        <v>97880</v>
+        <v>97875</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14635,21 +14635,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219874</v>
+        <v>219865</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14673,10 +14673,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693224</v>
+        <v>693227</v>
       </c>
       <c r="R123" t="n">
-        <v>6358167</v>
+        <v>6358157</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14740,10 +14740,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118772963</v>
+        <v>118772906</v>
       </c>
       <c r="B124" t="n">
-        <v>106776</v>
+        <v>97880</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14752,31 +14752,40 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220079</v>
+        <v>219874</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14785,10 +14794,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>692819</v>
+        <v>693224</v>
       </c>
       <c r="R124" t="n">
-        <v>6358429</v>
+        <v>6358167</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14852,10 +14861,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118772950</v>
+        <v>118772935</v>
       </c>
       <c r="B125" t="n">
-        <v>106120</v>
+        <v>97883</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14864,28 +14873,37 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221849</v>
+        <v>219875</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -14897,10 +14915,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>692872</v>
+        <v>693002</v>
       </c>
       <c r="R125" t="n">
-        <v>6358355</v>
+        <v>6358203</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14964,10 +14982,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118772939</v>
+        <v>118772900</v>
       </c>
       <c r="B126" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14980,39 +14998,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>692971</v>
+        <v>693224</v>
       </c>
       <c r="R126" t="n">
-        <v>6358246</v>
+        <v>6358167</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15076,7 +15089,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772955</v>
+        <v>118772940</v>
       </c>
       <c r="B127" t="n">
         <v>106120</v>
@@ -15121,10 +15134,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>692830</v>
+        <v>692961</v>
       </c>
       <c r="R127" t="n">
-        <v>6358401</v>
+        <v>6358267</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15188,7 +15201,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118772921</v>
+        <v>118772904</v>
       </c>
       <c r="B128" t="n">
         <v>97824</v>
@@ -15223,7 +15236,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15242,10 +15255,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693216</v>
+        <v>693224</v>
       </c>
       <c r="R128" t="n">
-        <v>6358159</v>
+        <v>6358167</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15309,10 +15322,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772899</v>
+        <v>118772898</v>
       </c>
       <c r="B129" t="n">
-        <v>97821</v>
+        <v>106120</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15321,52 +15334,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693184</v>
+        <v>692998</v>
       </c>
       <c r="R129" t="n">
-        <v>6358206</v>
+        <v>6358398</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15430,10 +15429,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772902</v>
+        <v>118772939</v>
       </c>
       <c r="B130" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15446,37 +15445,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>693210</v>
+        <v>692971</v>
       </c>
       <c r="R130" t="n">
-        <v>6358181</v>
+        <v>6358246</v>
       </c>
       <c r="S130" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15658,7 +15662,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772922</v>
+        <v>118772921</v>
       </c>
       <c r="B132" t="n">
         <v>97824</v>
@@ -15693,7 +15697,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15712,13 +15716,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693183</v>
+        <v>693216</v>
       </c>
       <c r="R132" t="n">
-        <v>6358169</v>
+        <v>6358159</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15779,10 +15783,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772954</v>
+        <v>118772963</v>
       </c>
       <c r="B133" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15795,27 +15799,27 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15824,10 +15828,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>692826</v>
+        <v>692819</v>
       </c>
       <c r="R133" t="n">
-        <v>6358398</v>
+        <v>6358429</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15891,10 +15895,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118772937</v>
+        <v>118772948</v>
       </c>
       <c r="B134" t="n">
-        <v>97882</v>
+        <v>106776</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15903,30 +15907,30 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15945,10 +15949,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>693008</v>
+        <v>692872</v>
       </c>
       <c r="R134" t="n">
-        <v>6358204</v>
+        <v>6358355</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16012,10 +16016,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118772938</v>
+        <v>118772895</v>
       </c>
       <c r="B135" t="n">
-        <v>106776</v>
+        <v>108453</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16028,39 +16032,50 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220079</v>
+        <v>220204</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>692997</v>
+        <v>692964</v>
       </c>
       <c r="R135" t="n">
-        <v>6358215</v>
+        <v>6358443</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16101,6 +16116,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -16124,10 +16140,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118772941</v>
+        <v>118772937</v>
       </c>
       <c r="B136" t="n">
-        <v>106120</v>
+        <v>97882</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16136,28 +16152,37 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221849</v>
+        <v>223621</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -16169,10 +16194,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>692930</v>
+        <v>693008</v>
       </c>
       <c r="R136" t="n">
-        <v>6358283</v>
+        <v>6358204</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -16236,10 +16261,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118773204</v>
+        <v>118772950</v>
       </c>
       <c r="B137" t="n">
-        <v>57993</v>
+        <v>106120</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16252,31 +16277,27 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -16285,13 +16306,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>693184</v>
+        <v>692872</v>
       </c>
       <c r="R137" t="n">
-        <v>6358206</v>
+        <v>6358355</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16334,7 +16355,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -16352,7 +16373,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118772896</v>
+        <v>118772902</v>
       </c>
       <c r="B138" t="n">
         <v>106776</v>
@@ -16392,13 +16413,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>692976</v>
+        <v>693210</v>
       </c>
       <c r="R138" t="n">
-        <v>6358428</v>
+        <v>6358181</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16459,10 +16480,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118772961</v>
+        <v>118772907</v>
       </c>
       <c r="B139" t="n">
-        <v>106120</v>
+        <v>97848</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16471,28 +16492,37 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221849</v>
+        <v>219811</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -16504,10 +16534,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>692821</v>
+        <v>693224</v>
       </c>
       <c r="R139" t="n">
-        <v>6358416</v>
+        <v>6358167</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16678,7 +16708,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118772900</v>
+        <v>118772896</v>
       </c>
       <c r="B141" t="n">
         <v>106776</v>
@@ -16718,10 +16748,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>693224</v>
+        <v>692976</v>
       </c>
       <c r="R141" t="n">
-        <v>6358167</v>
+        <v>6358428</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16785,7 +16815,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118772952</v>
+        <v>118772945</v>
       </c>
       <c r="B142" t="n">
         <v>106120</v>
@@ -16830,10 +16860,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>692835</v>
+        <v>692922</v>
       </c>
       <c r="R142" t="n">
-        <v>6358377</v>
+        <v>6358382</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16866,6 +16896,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16897,7 +16932,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118772947</v>
+        <v>118772946</v>
       </c>
       <c r="B143" t="n">
         <v>106120</v>
@@ -16942,10 +16977,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>692900</v>
+        <v>692894</v>
       </c>
       <c r="R143" t="n">
-        <v>6358363</v>
+        <v>6358376</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -17009,7 +17044,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118772946</v>
+        <v>118772952</v>
       </c>
       <c r="B144" t="n">
         <v>106120</v>
@@ -17054,10 +17089,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>692894</v>
+        <v>692835</v>
       </c>
       <c r="R144" t="n">
-        <v>6358376</v>
+        <v>6358377</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -17121,10 +17156,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118772942</v>
+        <v>118773204</v>
       </c>
       <c r="B145" t="n">
-        <v>97821</v>
+        <v>57993</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17133,40 +17168,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219797</v>
+        <v>103055</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -17175,13 +17205,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>692917</v>
+        <v>693184</v>
       </c>
       <c r="R145" t="n">
-        <v>6358307</v>
+        <v>6358206</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17224,7 +17254,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Betad skog, mest tall</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17242,10 +17272,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118772904</v>
+        <v>118772928</v>
       </c>
       <c r="B146" t="n">
-        <v>97824</v>
+        <v>109955</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17254,30 +17284,30 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219798</v>
+        <v>1243</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sammetsbockrot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pimpinella saxifraga subsp. nigra</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Mill.) Ces.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17296,10 +17326,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693224</v>
+        <v>693075</v>
       </c>
       <c r="R146" t="n">
-        <v>6358167</v>
+        <v>6358190</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -17363,10 +17393,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118772935</v>
+        <v>118772922</v>
       </c>
       <c r="B147" t="n">
-        <v>97883</v>
+        <v>97824</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17379,21 +17409,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>219875</v>
+        <v>219798</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -17408,7 +17438,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -17417,13 +17447,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693002</v>
+        <v>693183</v>
       </c>
       <c r="R147" t="n">
-        <v>6358203</v>
+        <v>6358169</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17484,7 +17514,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118772898</v>
+        <v>118772941</v>
       </c>
       <c r="B148" t="n">
         <v>106120</v>
@@ -17518,16 +17548,21 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>692998</v>
+        <v>692930</v>
       </c>
       <c r="R148" t="n">
-        <v>6358398</v>
+        <v>6358283</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -17591,10 +17626,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118772907</v>
+        <v>118772942</v>
       </c>
       <c r="B149" t="n">
-        <v>97848</v>
+        <v>97821</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17607,26 +17642,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219811</v>
+        <v>219797</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17645,13 +17680,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>693224</v>
+        <v>692917</v>
       </c>
       <c r="R149" t="n">
-        <v>6358167</v>
+        <v>6358307</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17712,10 +17747,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118772945</v>
+        <v>118772899</v>
       </c>
       <c r="B150" t="n">
-        <v>106120</v>
+        <v>97821</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17724,31 +17759,40 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -17757,10 +17801,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>692922</v>
+        <v>693184</v>
       </c>
       <c r="R150" t="n">
-        <v>6358382</v>
+        <v>6358206</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17793,11 +17837,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17829,10 +17868,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118773206</v>
+        <v>118772953</v>
       </c>
       <c r="B151" t="n">
-        <v>57993</v>
+        <v>106120</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17845,26 +17884,27 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17873,13 +17913,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>693183</v>
+        <v>692844</v>
       </c>
       <c r="R151" t="n">
-        <v>6358169</v>
+        <v>6358382</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17922,7 +17962,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Btad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -17940,10 +17980,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118772914</v>
+        <v>118772954</v>
       </c>
       <c r="B152" t="n">
-        <v>97848</v>
+        <v>106120</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17952,37 +17992,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>219811</v>
+        <v>221849</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17994,10 +18025,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>693225</v>
+        <v>692826</v>
       </c>
       <c r="R152" t="n">
-        <v>6358156</v>
+        <v>6358398</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18061,7 +18092,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118772953</v>
+        <v>118772961</v>
       </c>
       <c r="B153" t="n">
         <v>106120</v>
@@ -18106,10 +18137,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>692844</v>
+        <v>692821</v>
       </c>
       <c r="R153" t="n">
-        <v>6358382</v>
+        <v>6358416</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18173,10 +18204,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118772940</v>
+        <v>118772938</v>
       </c>
       <c r="B154" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18189,21 +18220,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18218,10 +18249,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>692961</v>
+        <v>692997</v>
       </c>
       <c r="R154" t="n">
-        <v>6358267</v>
+        <v>6358215</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18285,10 +18316,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118772895</v>
+        <v>118772962</v>
       </c>
       <c r="B155" t="n">
-        <v>108453</v>
+        <v>106120</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18301,16 +18332,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220204</v>
+        <v>221849</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -18318,33 +18349,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>692964</v>
+        <v>692819</v>
       </c>
       <c r="R155" t="n">
-        <v>6358443</v>
+        <v>6358429</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18385,7 +18405,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -18409,10 +18428,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118772912</v>
+        <v>118772914</v>
       </c>
       <c r="B156" t="n">
-        <v>97875</v>
+        <v>97848</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18425,26 +18444,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219865</v>
+        <v>219811</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18454,7 +18473,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -18463,10 +18482,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>693227</v>
+        <v>693225</v>
       </c>
       <c r="R156" t="n">
-        <v>6358157</v>
+        <v>6358156</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18530,7 +18549,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118772962</v>
+        <v>118772947</v>
       </c>
       <c r="B157" t="n">
         <v>106120</v>
@@ -18575,10 +18594,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>692819</v>
+        <v>692900</v>
       </c>
       <c r="R157" t="n">
-        <v>6358429</v>
+        <v>6358363</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18642,10 +18661,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118772948</v>
+        <v>118773206</v>
       </c>
       <c r="B158" t="n">
-        <v>106776</v>
+        <v>57993</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18658,36 +18677,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220079</v>
+        <v>103055</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18696,13 +18705,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>692872</v>
+        <v>693183</v>
       </c>
       <c r="R158" t="n">
-        <v>6358355</v>
+        <v>6358169</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18745,7 +18754,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Btad skog, mest tall</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -18763,10 +18772,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118772928</v>
+        <v>118772955</v>
       </c>
       <c r="B159" t="n">
-        <v>109955</v>
+        <v>106120</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18775,40 +18784,31 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1243</v>
+        <v>221849</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sammetsbockrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pimpinella saxifraga subsp. nigra</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Mill.) Ces.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18817,10 +18817,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693075</v>
+        <v>692830</v>
       </c>
       <c r="R159" t="n">
-        <v>6358190</v>
+        <v>6358401</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -15662,10 +15662,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772921</v>
+        <v>118772963</v>
       </c>
       <c r="B132" t="n">
-        <v>97824</v>
+        <v>106776</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15674,40 +15674,31 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15716,10 +15707,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693216</v>
+        <v>692819</v>
       </c>
       <c r="R132" t="n">
-        <v>6358159</v>
+        <v>6358429</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15783,10 +15774,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772963</v>
+        <v>118772921</v>
       </c>
       <c r="B133" t="n">
-        <v>106776</v>
+        <v>97824</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15795,31 +15786,40 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15828,10 +15828,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>692819</v>
+        <v>693216</v>
       </c>
       <c r="R133" t="n">
-        <v>6358429</v>
+        <v>6358159</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -18204,10 +18204,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118772938</v>
+        <v>118772962</v>
       </c>
       <c r="B154" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18220,21 +18220,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18249,10 +18249,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>692997</v>
+        <v>692819</v>
       </c>
       <c r="R154" t="n">
-        <v>6358215</v>
+        <v>6358429</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18316,10 +18316,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118772962</v>
+        <v>118772938</v>
       </c>
       <c r="B155" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18332,21 +18332,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18361,10 +18361,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>692819</v>
+        <v>692997</v>
       </c>
       <c r="R155" t="n">
-        <v>6358429</v>
+        <v>6358215</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18661,10 +18661,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118773206</v>
+        <v>118772955</v>
       </c>
       <c r="B158" t="n">
-        <v>57993</v>
+        <v>106120</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18677,26 +18677,27 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18705,13 +18706,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>693183</v>
+        <v>692830</v>
       </c>
       <c r="R158" t="n">
-        <v>6358169</v>
+        <v>6358401</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18754,7 +18755,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>Btad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -18772,10 +18773,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118772955</v>
+        <v>118773206</v>
       </c>
       <c r="B159" t="n">
-        <v>106120</v>
+        <v>57993</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18788,27 +18789,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18817,13 +18817,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>692830</v>
+        <v>693183</v>
       </c>
       <c r="R159" t="n">
-        <v>6358401</v>
+        <v>6358169</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Btad skog, mest tall</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -14619,10 +14619,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772912</v>
+        <v>118772953</v>
       </c>
       <c r="B123" t="n">
-        <v>97875</v>
+        <v>106120</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14631,20 +14631,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219865</v>
+        <v>221849</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14652,19 +14652,10 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14673,10 +14664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693227</v>
+        <v>692844</v>
       </c>
       <c r="R123" t="n">
-        <v>6358157</v>
+        <v>6358382</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14740,10 +14731,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118772906</v>
+        <v>118772905</v>
       </c>
       <c r="B124" t="n">
-        <v>97880</v>
+        <v>106776</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14752,42 +14743,28 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219874</v>
+        <v>220079</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
@@ -14861,10 +14838,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118772935</v>
+        <v>118772898</v>
       </c>
       <c r="B125" t="n">
-        <v>97883</v>
+        <v>106120</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14873,52 +14850,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219875</v>
+        <v>221849</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>693002</v>
+        <v>692998</v>
       </c>
       <c r="R125" t="n">
-        <v>6358203</v>
+        <v>6358398</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14982,10 +14945,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118772900</v>
+        <v>118772912</v>
       </c>
       <c r="B126" t="n">
-        <v>106776</v>
+        <v>97875</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14994,38 +14957,52 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220079</v>
+        <v>219865</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>693224</v>
+        <v>693227</v>
       </c>
       <c r="R126" t="n">
-        <v>6358167</v>
+        <v>6358157</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15089,10 +15066,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772940</v>
+        <v>118772942</v>
       </c>
       <c r="B127" t="n">
-        <v>106120</v>
+        <v>97821</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15101,28 +15078,37 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15134,13 +15120,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>692961</v>
+        <v>692917</v>
       </c>
       <c r="R127" t="n">
-        <v>6358267</v>
+        <v>6358307</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15201,10 +15187,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118772904</v>
+        <v>118773204</v>
       </c>
       <c r="B128" t="n">
-        <v>97824</v>
+        <v>57993</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15213,25 +15199,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>103055</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15239,14 +15225,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -15255,13 +15236,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693224</v>
+        <v>693184</v>
       </c>
       <c r="R128" t="n">
-        <v>6358167</v>
+        <v>6358206</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15304,7 +15285,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Betad skog, mest tall</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15315,17 +15296,17 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Brita Svensson, Bengt Carlsson, Jörgen Petersson, Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772898</v>
+        <v>118772914</v>
       </c>
       <c r="B129" t="n">
-        <v>106120</v>
+        <v>97848</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15334,38 +15315,52 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221849</v>
+        <v>219811</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>692998</v>
+        <v>693225</v>
       </c>
       <c r="R129" t="n">
-        <v>6358398</v>
+        <v>6358156</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15429,10 +15424,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772939</v>
+        <v>118772895</v>
       </c>
       <c r="B130" t="n">
-        <v>106120</v>
+        <v>108453</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15445,16 +15440,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -15462,22 +15457,33 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>692971</v>
+        <v>692964</v>
       </c>
       <c r="R130" t="n">
-        <v>6358246</v>
+        <v>6358443</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -15518,6 +15524,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -15541,10 +15548,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772924</v>
+        <v>118772899</v>
       </c>
       <c r="B131" t="n">
-        <v>97875</v>
+        <v>97821</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15557,21 +15564,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219865</v>
+        <v>219797</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -15586,7 +15593,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -15595,10 +15602,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693132</v>
+        <v>693184</v>
       </c>
       <c r="R131" t="n">
-        <v>6358167</v>
+        <v>6358206</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -15662,10 +15669,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772963</v>
+        <v>118772907</v>
       </c>
       <c r="B132" t="n">
-        <v>106776</v>
+        <v>97848</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15674,31 +15681,40 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220079</v>
+        <v>219811</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15707,10 +15723,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>692819</v>
+        <v>693224</v>
       </c>
       <c r="R132" t="n">
-        <v>6358429</v>
+        <v>6358167</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15774,10 +15790,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772921</v>
+        <v>118772963</v>
       </c>
       <c r="B133" t="n">
-        <v>97824</v>
+        <v>106776</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15786,40 +15802,31 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15828,10 +15835,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>693216</v>
+        <v>692819</v>
       </c>
       <c r="R133" t="n">
-        <v>6358159</v>
+        <v>6358429</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15895,10 +15902,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118772948</v>
+        <v>118772955</v>
       </c>
       <c r="B134" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15911,33 +15918,24 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15949,10 +15947,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>692872</v>
+        <v>692830</v>
       </c>
       <c r="R134" t="n">
-        <v>6358355</v>
+        <v>6358401</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16016,10 +16014,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118772895</v>
+        <v>118772938</v>
       </c>
       <c r="B135" t="n">
-        <v>108453</v>
+        <v>106776</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16032,50 +16030,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220204</v>
+        <v>220079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>692964</v>
+        <v>692997</v>
       </c>
       <c r="R135" t="n">
-        <v>6358443</v>
+        <v>6358215</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16116,7 +16103,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -16140,10 +16126,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118772937</v>
+        <v>118772954</v>
       </c>
       <c r="B136" t="n">
-        <v>97882</v>
+        <v>106120</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16152,37 +16138,28 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>223621</v>
+        <v>221849</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -16194,10 +16171,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>693008</v>
+        <v>692826</v>
       </c>
       <c r="R136" t="n">
-        <v>6358204</v>
+        <v>6358398</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -16261,10 +16238,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118772950</v>
+        <v>118772928</v>
       </c>
       <c r="B137" t="n">
-        <v>106120</v>
+        <v>109955</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16273,31 +16250,40 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>221849</v>
+        <v>1243</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sammetsbockrot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Pimpinella saxifraga subsp. nigra</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Mill.) Ces.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -16306,10 +16292,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>692872</v>
+        <v>693075</v>
       </c>
       <c r="R137" t="n">
-        <v>6358355</v>
+        <v>6358190</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16373,10 +16359,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118772902</v>
+        <v>118772939</v>
       </c>
       <c r="B138" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16389,37 +16375,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>693210</v>
+        <v>692971</v>
       </c>
       <c r="R138" t="n">
-        <v>6358181</v>
+        <v>6358246</v>
       </c>
       <c r="S138" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16480,10 +16471,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118772907</v>
+        <v>118772935</v>
       </c>
       <c r="B139" t="n">
-        <v>97848</v>
+        <v>97883</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16496,26 +16487,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219811</v>
+        <v>219875</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16534,10 +16525,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>693224</v>
+        <v>693002</v>
       </c>
       <c r="R139" t="n">
-        <v>6358167</v>
+        <v>6358203</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16601,10 +16592,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118772926</v>
+        <v>118772940</v>
       </c>
       <c r="B140" t="n">
-        <v>109751</v>
+        <v>106120</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16613,20 +16604,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219677</v>
+        <v>221849</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -16635,19 +16626,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>693101</v>
+        <v>692961</v>
       </c>
       <c r="R140" t="n">
-        <v>6358192</v>
+        <v>6358267</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16708,10 +16704,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118772896</v>
+        <v>118772941</v>
       </c>
       <c r="B141" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16724,34 +16720,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>692976</v>
+        <v>692930</v>
       </c>
       <c r="R141" t="n">
-        <v>6358428</v>
+        <v>6358283</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16932,7 +16933,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118772946</v>
+        <v>118772952</v>
       </c>
       <c r="B143" t="n">
         <v>106120</v>
@@ -16977,10 +16978,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>692894</v>
+        <v>692835</v>
       </c>
       <c r="R143" t="n">
-        <v>6358376</v>
+        <v>6358377</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -17044,7 +17045,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118772952</v>
+        <v>118772947</v>
       </c>
       <c r="B144" t="n">
         <v>106120</v>
@@ -17089,10 +17090,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>692835</v>
+        <v>692900</v>
       </c>
       <c r="R144" t="n">
-        <v>6358377</v>
+        <v>6358363</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -17156,10 +17157,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118773204</v>
+        <v>118772950</v>
       </c>
       <c r="B145" t="n">
-        <v>57993</v>
+        <v>106120</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17172,31 +17173,27 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -17205,13 +17202,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693184</v>
+        <v>692872</v>
       </c>
       <c r="R145" t="n">
-        <v>6358206</v>
+        <v>6358355</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17254,7 +17251,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17272,10 +17269,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118772928</v>
+        <v>118772926</v>
       </c>
       <c r="B146" t="n">
-        <v>109955</v>
+        <v>109751</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17284,55 +17281,41 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1243</v>
+        <v>219677</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sammetsbockrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pimpinella saxifraga subsp. nigra</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Mill.) Ces.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693075</v>
+        <v>693101</v>
       </c>
       <c r="R146" t="n">
-        <v>6358190</v>
+        <v>6358192</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17393,10 +17376,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118772922</v>
+        <v>118772906</v>
       </c>
       <c r="B147" t="n">
-        <v>97824</v>
+        <v>97880</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17409,21 +17392,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>219798</v>
+        <v>219874</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -17438,7 +17421,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -17447,13 +17430,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693183</v>
+        <v>693224</v>
       </c>
       <c r="R147" t="n">
-        <v>6358169</v>
+        <v>6358167</v>
       </c>
       <c r="S147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17514,10 +17497,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118772941</v>
+        <v>118772948</v>
       </c>
       <c r="B148" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17530,24 +17513,33 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17559,10 +17551,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>692930</v>
+        <v>692872</v>
       </c>
       <c r="R148" t="n">
-        <v>6358283</v>
+        <v>6358355</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -17626,10 +17618,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118772942</v>
+        <v>118772896</v>
       </c>
       <c r="B149" t="n">
-        <v>97821</v>
+        <v>106776</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17638,55 +17630,41 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>692917</v>
+        <v>692976</v>
       </c>
       <c r="R149" t="n">
-        <v>6358307</v>
+        <v>6358428</v>
       </c>
       <c r="S149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17747,10 +17725,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118772899</v>
+        <v>118772921</v>
       </c>
       <c r="B150" t="n">
-        <v>97821</v>
+        <v>97824</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17763,26 +17741,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17801,10 +17779,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>693184</v>
+        <v>693216</v>
       </c>
       <c r="R150" t="n">
-        <v>6358206</v>
+        <v>6358159</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17868,10 +17846,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118772953</v>
+        <v>118773206</v>
       </c>
       <c r="B151" t="n">
-        <v>106120</v>
+        <v>57993</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17884,27 +17862,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17913,13 +17890,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>692844</v>
+        <v>693183</v>
       </c>
       <c r="R151" t="n">
-        <v>6358382</v>
+        <v>6358169</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17962,7 +17939,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Btad skog, mest tall</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -17973,17 +17950,17 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Brita Svensson, Bengt Carlsson, Jörgen Petersson, Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118772954</v>
+        <v>118772902</v>
       </c>
       <c r="B152" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17996,42 +17973,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>692826</v>
+        <v>693210</v>
       </c>
       <c r="R152" t="n">
-        <v>6358398</v>
+        <v>6358181</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18204,10 +18176,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118772962</v>
+        <v>118772924</v>
       </c>
       <c r="B154" t="n">
-        <v>106120</v>
+        <v>97875</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18216,20 +18188,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221849</v>
+        <v>219865</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -18237,10 +18209,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18249,10 +18230,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>692819</v>
+        <v>693132</v>
       </c>
       <c r="R154" t="n">
-        <v>6358429</v>
+        <v>6358167</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18316,10 +18297,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118772938</v>
+        <v>118772904</v>
       </c>
       <c r="B155" t="n">
-        <v>106776</v>
+        <v>97824</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18328,31 +18309,40 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -18361,10 +18351,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>692997</v>
+        <v>693224</v>
       </c>
       <c r="R155" t="n">
-        <v>6358215</v>
+        <v>6358167</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18428,10 +18418,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118772914</v>
+        <v>118772937</v>
       </c>
       <c r="B156" t="n">
-        <v>97848</v>
+        <v>97882</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18444,26 +18434,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219811</v>
+        <v>223621</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18482,10 +18472,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>693225</v>
+        <v>693008</v>
       </c>
       <c r="R156" t="n">
-        <v>6358156</v>
+        <v>6358204</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18549,7 +18539,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118772947</v>
+        <v>118772962</v>
       </c>
       <c r="B157" t="n">
         <v>106120</v>
@@ -18594,10 +18584,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>692900</v>
+        <v>692819</v>
       </c>
       <c r="R157" t="n">
-        <v>6358363</v>
+        <v>6358429</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18661,10 +18651,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118772955</v>
+        <v>118772922</v>
       </c>
       <c r="B158" t="n">
-        <v>106120</v>
+        <v>97824</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18673,31 +18663,40 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18706,13 +18705,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>692830</v>
+        <v>693183</v>
       </c>
       <c r="R158" t="n">
-        <v>6358401</v>
+        <v>6358169</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18773,10 +18772,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118773206</v>
+        <v>118772946</v>
       </c>
       <c r="B159" t="n">
-        <v>57993</v>
+        <v>106120</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18789,26 +18788,27 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18817,13 +18817,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693183</v>
+        <v>692894</v>
       </c>
       <c r="R159" t="n">
-        <v>6358169</v>
+        <v>6358376</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>Btad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -14619,10 +14619,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772953</v>
+        <v>118772921</v>
       </c>
       <c r="B123" t="n">
-        <v>106120</v>
+        <v>97831</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14631,31 +14631,40 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14664,10 +14673,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>692844</v>
+        <v>693216</v>
       </c>
       <c r="R123" t="n">
-        <v>6358382</v>
+        <v>6358159</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14731,10 +14740,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118772905</v>
+        <v>118772941</v>
       </c>
       <c r="B124" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14747,34 +14756,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>693224</v>
+        <v>692930</v>
       </c>
       <c r="R124" t="n">
-        <v>6358167</v>
+        <v>6358283</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14838,10 +14852,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118772898</v>
+        <v>118772906</v>
       </c>
       <c r="B125" t="n">
-        <v>106120</v>
+        <v>97887</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14850,38 +14864,52 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221849</v>
+        <v>219874</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>692998</v>
+        <v>693224</v>
       </c>
       <c r="R125" t="n">
-        <v>6358398</v>
+        <v>6358167</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14945,10 +14973,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118772912</v>
+        <v>118772940</v>
       </c>
       <c r="B126" t="n">
-        <v>97875</v>
+        <v>106127</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14957,20 +14985,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219865</v>
+        <v>221849</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -14978,19 +15006,10 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14999,10 +15018,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>693227</v>
+        <v>692961</v>
       </c>
       <c r="R126" t="n">
-        <v>6358157</v>
+        <v>6358267</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15066,10 +15085,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772942</v>
+        <v>118772937</v>
       </c>
       <c r="B127" t="n">
-        <v>97821</v>
+        <v>97889</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15082,26 +15101,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219797</v>
+        <v>223621</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15120,13 +15139,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>692917</v>
+        <v>693008</v>
       </c>
       <c r="R127" t="n">
-        <v>6358307</v>
+        <v>6358204</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15187,10 +15206,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118773204</v>
+        <v>118772907</v>
       </c>
       <c r="B128" t="n">
-        <v>57993</v>
+        <v>97855</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15199,35 +15218,40 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>103055</v>
+        <v>219811</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -15236,13 +15260,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693184</v>
+        <v>693224</v>
       </c>
       <c r="R128" t="n">
-        <v>6358206</v>
+        <v>6358167</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15285,7 +15309,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15296,17 +15320,17 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Brita Svensson, Bengt Carlsson, Jörgen Petersson, Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772914</v>
+        <v>118772924</v>
       </c>
       <c r="B129" t="n">
-        <v>97848</v>
+        <v>97882</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15319,26 +15343,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219811</v>
+        <v>219865</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15348,7 +15372,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -15357,10 +15381,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693225</v>
+        <v>693132</v>
       </c>
       <c r="R129" t="n">
-        <v>6358156</v>
+        <v>6358167</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15424,10 +15448,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772895</v>
+        <v>118772922</v>
       </c>
       <c r="B130" t="n">
-        <v>108453</v>
+        <v>97831</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15436,25 +15460,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220204</v>
+        <v>219798</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -15472,21 +15496,19 @@
           <t>blomknopp</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>692964</v>
+        <v>693183</v>
       </c>
       <c r="R130" t="n">
-        <v>6358443</v>
+        <v>6358169</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15524,7 +15546,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -15548,10 +15569,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772899</v>
+        <v>118772926</v>
       </c>
       <c r="B131" t="n">
-        <v>97821</v>
+        <v>109758</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15564,51 +15585,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219797</v>
+        <v>219677</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693184</v>
+        <v>693101</v>
       </c>
       <c r="R131" t="n">
-        <v>6358206</v>
+        <v>6358192</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15669,10 +15676,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772907</v>
+        <v>118772942</v>
       </c>
       <c r="B132" t="n">
-        <v>97848</v>
+        <v>97828</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15685,26 +15692,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219811</v>
+        <v>219797</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15723,13 +15730,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693224</v>
+        <v>692917</v>
       </c>
       <c r="R132" t="n">
-        <v>6358167</v>
+        <v>6358307</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15790,10 +15797,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772963</v>
+        <v>118772945</v>
       </c>
       <c r="B133" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15806,27 +15813,27 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15835,10 +15842,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>692819</v>
+        <v>692922</v>
       </c>
       <c r="R133" t="n">
-        <v>6358429</v>
+        <v>6358382</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15871,6 +15878,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15902,10 +15914,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118772955</v>
+        <v>118772946</v>
       </c>
       <c r="B134" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15947,10 +15959,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>692830</v>
+        <v>692894</v>
       </c>
       <c r="R134" t="n">
-        <v>6358401</v>
+        <v>6358376</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16014,10 +16026,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118772938</v>
+        <v>118772952</v>
       </c>
       <c r="B135" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16030,21 +16042,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16059,10 +16071,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>692997</v>
+        <v>692835</v>
       </c>
       <c r="R135" t="n">
-        <v>6358215</v>
+        <v>6358377</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16129,7 +16141,7 @@
         <v>118772954</v>
       </c>
       <c r="B136" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16238,10 +16250,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118772928</v>
+        <v>118772963</v>
       </c>
       <c r="B137" t="n">
-        <v>109955</v>
+        <v>106783</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16250,40 +16262,31 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1243</v>
+        <v>220079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sammetsbockrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pimpinella saxifraga subsp. nigra</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Mill.) Ces.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -16292,10 +16295,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>693075</v>
+        <v>692819</v>
       </c>
       <c r="R137" t="n">
-        <v>6358190</v>
+        <v>6358429</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16359,10 +16362,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118772939</v>
+        <v>118772948</v>
       </c>
       <c r="B138" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16375,24 +16378,33 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -16404,10 +16416,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>692971</v>
+        <v>692872</v>
       </c>
       <c r="R138" t="n">
-        <v>6358246</v>
+        <v>6358355</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16471,10 +16483,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118772935</v>
+        <v>118772896</v>
       </c>
       <c r="B139" t="n">
-        <v>97883</v>
+        <v>106783</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16483,52 +16495,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>693002</v>
+        <v>692976</v>
       </c>
       <c r="R139" t="n">
-        <v>6358203</v>
+        <v>6358428</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16592,10 +16590,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118772940</v>
+        <v>118772912</v>
       </c>
       <c r="B140" t="n">
-        <v>106120</v>
+        <v>97882</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16604,20 +16602,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221849</v>
+        <v>219865</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -16625,10 +16623,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16637,10 +16644,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>692961</v>
+        <v>693227</v>
       </c>
       <c r="R140" t="n">
-        <v>6358267</v>
+        <v>6358157</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16704,10 +16711,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118772941</v>
+        <v>118772935</v>
       </c>
       <c r="B141" t="n">
-        <v>106120</v>
+        <v>97890</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16716,28 +16723,37 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221849</v>
+        <v>219875</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -16749,10 +16765,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>692930</v>
+        <v>693002</v>
       </c>
       <c r="R141" t="n">
-        <v>6358283</v>
+        <v>6358203</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16816,10 +16832,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118772945</v>
+        <v>118772938</v>
       </c>
       <c r="B142" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16832,21 +16848,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16861,10 +16877,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>692922</v>
+        <v>692997</v>
       </c>
       <c r="R142" t="n">
-        <v>6358382</v>
+        <v>6358215</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16897,11 +16913,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16933,10 +16944,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118772952</v>
+        <v>118772939</v>
       </c>
       <c r="B143" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16978,10 +16989,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>692835</v>
+        <v>692971</v>
       </c>
       <c r="R143" t="n">
-        <v>6358377</v>
+        <v>6358246</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -17045,10 +17056,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118772947</v>
+        <v>118772962</v>
       </c>
       <c r="B144" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17090,10 +17101,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>692900</v>
+        <v>692819</v>
       </c>
       <c r="R144" t="n">
-        <v>6358363</v>
+        <v>6358429</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -17157,10 +17168,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118772950</v>
+        <v>118772955</v>
       </c>
       <c r="B145" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17202,10 +17213,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>692872</v>
+        <v>692830</v>
       </c>
       <c r="R145" t="n">
-        <v>6358355</v>
+        <v>6358401</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -17269,10 +17280,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118772926</v>
+        <v>118772904</v>
       </c>
       <c r="B146" t="n">
-        <v>109751</v>
+        <v>97831</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17285,37 +17296,51 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693101</v>
+        <v>693224</v>
       </c>
       <c r="R146" t="n">
-        <v>6358192</v>
+        <v>6358167</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17376,10 +17401,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118772906</v>
+        <v>118772905</v>
       </c>
       <c r="B147" t="n">
-        <v>97880</v>
+        <v>106783</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17388,42 +17413,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>219874</v>
+        <v>220079</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
@@ -17497,10 +17508,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118772948</v>
+        <v>118772898</v>
       </c>
       <c r="B148" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17513,48 +17524,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>692872</v>
+        <v>692998</v>
       </c>
       <c r="R148" t="n">
-        <v>6358355</v>
+        <v>6358398</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -17618,10 +17615,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118772896</v>
+        <v>118773204</v>
       </c>
       <c r="B149" t="n">
-        <v>106776</v>
+        <v>57993</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17634,37 +17631,46 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220079</v>
+        <v>103055</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>692976</v>
+        <v>693184</v>
       </c>
       <c r="R149" t="n">
-        <v>6358428</v>
+        <v>6358206</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17707,7 +17713,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Betad skog, mest tall</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -17725,10 +17731,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118772921</v>
+        <v>118772928</v>
       </c>
       <c r="B150" t="n">
-        <v>97824</v>
+        <v>109962</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17737,30 +17743,30 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>219798</v>
+        <v>1243</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sammetsbockrot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pimpinella saxifraga subsp. nigra</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Mill.) Ces.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17779,10 +17785,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>693216</v>
+        <v>693075</v>
       </c>
       <c r="R150" t="n">
-        <v>6358159</v>
+        <v>6358190</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17846,10 +17852,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118773206</v>
+        <v>118772914</v>
       </c>
       <c r="B151" t="n">
-        <v>57993</v>
+        <v>97855</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17858,30 +17864,40 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>103055</v>
+        <v>219811</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17890,13 +17906,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>693183</v>
+        <v>693225</v>
       </c>
       <c r="R151" t="n">
-        <v>6358169</v>
+        <v>6358156</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17939,7 +17955,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Btad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -17950,17 +17966,17 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Brita Svensson, Bengt Carlsson, Jörgen Petersson, Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118772902</v>
+        <v>118772950</v>
       </c>
       <c r="B152" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17973,37 +17989,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>693210</v>
+        <v>692872</v>
       </c>
       <c r="R152" t="n">
-        <v>6358181</v>
+        <v>6358355</v>
       </c>
       <c r="S152" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18064,10 +18085,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118772961</v>
+        <v>118773206</v>
       </c>
       <c r="B153" t="n">
-        <v>106120</v>
+        <v>57993</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18080,27 +18101,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -18109,13 +18129,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>692821</v>
+        <v>693183</v>
       </c>
       <c r="R153" t="n">
-        <v>6358416</v>
+        <v>6358169</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18158,7 +18178,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Btad skog, mest tall</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18176,10 +18196,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118772924</v>
+        <v>118772961</v>
       </c>
       <c r="B154" t="n">
-        <v>97875</v>
+        <v>106127</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18188,20 +18208,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>219865</v>
+        <v>221849</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -18209,19 +18229,10 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18230,10 +18241,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>693132</v>
+        <v>692821</v>
       </c>
       <c r="R154" t="n">
-        <v>6358167</v>
+        <v>6358416</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18297,10 +18308,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118772904</v>
+        <v>118772953</v>
       </c>
       <c r="B155" t="n">
-        <v>97824</v>
+        <v>106127</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18309,40 +18320,31 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -18351,10 +18353,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>693224</v>
+        <v>692844</v>
       </c>
       <c r="R155" t="n">
-        <v>6358167</v>
+        <v>6358382</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18418,10 +18420,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118772937</v>
+        <v>118772947</v>
       </c>
       <c r="B156" t="n">
-        <v>97882</v>
+        <v>106127</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18430,37 +18432,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>223621</v>
+        <v>221849</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18472,10 +18465,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>693008</v>
+        <v>692900</v>
       </c>
       <c r="R156" t="n">
-        <v>6358204</v>
+        <v>6358363</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18539,10 +18532,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118772962</v>
+        <v>118772895</v>
       </c>
       <c r="B157" t="n">
-        <v>106120</v>
+        <v>108460</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18555,16 +18548,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -18572,22 +18565,33 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>692819</v>
+        <v>692964</v>
       </c>
       <c r="R157" t="n">
-        <v>6358429</v>
+        <v>6358443</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18628,6 +18632,7 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18651,10 +18656,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118772922</v>
+        <v>118772899</v>
       </c>
       <c r="B158" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18667,26 +18672,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18705,13 +18710,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>693183</v>
+        <v>693184</v>
       </c>
       <c r="R158" t="n">
-        <v>6358169</v>
+        <v>6358206</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18772,10 +18777,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118772946</v>
+        <v>118772902</v>
       </c>
       <c r="B159" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18788,42 +18793,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>692894</v>
+        <v>693210</v>
       </c>
       <c r="R159" t="n">
-        <v>6358376</v>
+        <v>6358181</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -15448,10 +15448,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772922</v>
+        <v>118772945</v>
       </c>
       <c r="B130" t="n">
-        <v>97831</v>
+        <v>106127</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15460,40 +15460,31 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -15502,13 +15493,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>693183</v>
+        <v>692922</v>
       </c>
       <c r="R130" t="n">
-        <v>6358169</v>
+        <v>6358382</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15538,6 +15529,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15569,10 +15565,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772926</v>
+        <v>118772922</v>
       </c>
       <c r="B131" t="n">
-        <v>109758</v>
+        <v>97831</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15585,37 +15581,51 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693101</v>
+        <v>693183</v>
       </c>
       <c r="R131" t="n">
-        <v>6358192</v>
+        <v>6358169</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15676,10 +15686,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772942</v>
+        <v>118772926</v>
       </c>
       <c r="B132" t="n">
-        <v>97828</v>
+        <v>109758</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15692,51 +15702,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219797</v>
+        <v>219677</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>692917</v>
+        <v>693101</v>
       </c>
       <c r="R132" t="n">
-        <v>6358307</v>
+        <v>6358192</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15797,10 +15793,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772945</v>
+        <v>118772942</v>
       </c>
       <c r="B133" t="n">
-        <v>106127</v>
+        <v>97828</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15809,28 +15805,37 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15842,13 +15847,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>692922</v>
+        <v>692917</v>
       </c>
       <c r="R133" t="n">
-        <v>6358382</v>
+        <v>6358307</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15878,11 +15883,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD133" t="b">

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -14619,10 +14619,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772921</v>
+        <v>118772926</v>
       </c>
       <c r="B123" t="n">
-        <v>97831</v>
+        <v>109758</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14635,51 +14635,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693216</v>
+        <v>693101</v>
       </c>
       <c r="R123" t="n">
-        <v>6358159</v>
+        <v>6358192</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14740,7 +14726,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118772941</v>
+        <v>118772945</v>
       </c>
       <c r="B124" t="n">
         <v>106127</v>
@@ -14785,10 +14771,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>692930</v>
+        <v>692922</v>
       </c>
       <c r="R124" t="n">
-        <v>6358283</v>
+        <v>6358382</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14821,6 +14807,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14852,10 +14843,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118772906</v>
+        <v>118772953</v>
       </c>
       <c r="B125" t="n">
-        <v>97887</v>
+        <v>106127</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14864,40 +14855,31 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219874</v>
+        <v>221849</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14906,10 +14888,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>693224</v>
+        <v>692844</v>
       </c>
       <c r="R125" t="n">
-        <v>6358167</v>
+        <v>6358382</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14973,10 +14955,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118772940</v>
+        <v>118772896</v>
       </c>
       <c r="B126" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14989,39 +14971,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>692961</v>
+        <v>692976</v>
       </c>
       <c r="R126" t="n">
-        <v>6358267</v>
+        <v>6358428</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15085,10 +15062,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772937</v>
+        <v>118772924</v>
       </c>
       <c r="B127" t="n">
-        <v>97889</v>
+        <v>97882</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15101,26 +15078,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>223621</v>
+        <v>219865</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15130,7 +15107,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -15139,10 +15116,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>693008</v>
+        <v>693132</v>
       </c>
       <c r="R127" t="n">
-        <v>6358204</v>
+        <v>6358167</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15206,10 +15183,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118772907</v>
+        <v>118772922</v>
       </c>
       <c r="B128" t="n">
-        <v>97855</v>
+        <v>97831</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15222,26 +15199,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15251,7 +15228,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -15260,13 +15237,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693224</v>
+        <v>693183</v>
       </c>
       <c r="R128" t="n">
-        <v>6358167</v>
+        <v>6358169</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15327,10 +15304,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772924</v>
+        <v>118772947</v>
       </c>
       <c r="B129" t="n">
-        <v>97882</v>
+        <v>106127</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15339,20 +15316,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219865</v>
+        <v>221849</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -15360,19 +15337,10 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -15381,10 +15349,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693132</v>
+        <v>692900</v>
       </c>
       <c r="R129" t="n">
-        <v>6358167</v>
+        <v>6358363</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15448,10 +15416,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772945</v>
+        <v>118772921</v>
       </c>
       <c r="B130" t="n">
-        <v>106127</v>
+        <v>97831</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15460,31 +15428,40 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -15493,10 +15470,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>692922</v>
+        <v>693216</v>
       </c>
       <c r="R130" t="n">
-        <v>6358382</v>
+        <v>6358159</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -15529,11 +15506,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15565,10 +15537,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772922</v>
+        <v>118772914</v>
       </c>
       <c r="B131" t="n">
-        <v>97831</v>
+        <v>97855</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15581,26 +15553,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -15610,7 +15582,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -15619,13 +15591,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693183</v>
+        <v>693225</v>
       </c>
       <c r="R131" t="n">
-        <v>6358169</v>
+        <v>6358156</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15686,10 +15658,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772926</v>
+        <v>118772962</v>
       </c>
       <c r="B132" t="n">
-        <v>109758</v>
+        <v>106127</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15698,20 +15670,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219677</v>
+        <v>221849</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -15720,19 +15692,24 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693101</v>
+        <v>692819</v>
       </c>
       <c r="R132" t="n">
-        <v>6358192</v>
+        <v>6358429</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15793,10 +15770,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772942</v>
+        <v>118772941</v>
       </c>
       <c r="B133" t="n">
-        <v>97828</v>
+        <v>106127</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15805,37 +15782,28 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15847,13 +15815,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>692917</v>
+        <v>692930</v>
       </c>
       <c r="R133" t="n">
-        <v>6358307</v>
+        <v>6358283</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15914,7 +15882,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118772946</v>
+        <v>118772954</v>
       </c>
       <c r="B134" t="n">
         <v>106127</v>
@@ -15959,10 +15927,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>692894</v>
+        <v>692826</v>
       </c>
       <c r="R134" t="n">
-        <v>6358376</v>
+        <v>6358398</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16026,10 +15994,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118772952</v>
+        <v>118772912</v>
       </c>
       <c r="B135" t="n">
-        <v>106127</v>
+        <v>97882</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16038,20 +16006,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221849</v>
+        <v>219865</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -16059,10 +16027,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16071,10 +16048,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>692835</v>
+        <v>693227</v>
       </c>
       <c r="R135" t="n">
-        <v>6358377</v>
+        <v>6358157</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16138,10 +16115,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118772954</v>
+        <v>118772906</v>
       </c>
       <c r="B136" t="n">
-        <v>106127</v>
+        <v>97887</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16150,31 +16127,40 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221849</v>
+        <v>219874</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -16183,10 +16169,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>692826</v>
+        <v>693224</v>
       </c>
       <c r="R136" t="n">
-        <v>6358398</v>
+        <v>6358167</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -16250,10 +16236,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118772963</v>
+        <v>118772907</v>
       </c>
       <c r="B137" t="n">
-        <v>106783</v>
+        <v>97855</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16262,31 +16248,40 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220079</v>
+        <v>219811</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -16295,10 +16290,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>692819</v>
+        <v>693224</v>
       </c>
       <c r="R137" t="n">
-        <v>6358429</v>
+        <v>6358167</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16362,10 +16357,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118772948</v>
+        <v>118772898</v>
       </c>
       <c r="B138" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16378,48 +16373,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>692872</v>
+        <v>692998</v>
       </c>
       <c r="R138" t="n">
-        <v>6358355</v>
+        <v>6358398</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16483,7 +16464,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118772896</v>
+        <v>118772963</v>
       </c>
       <c r="B139" t="n">
         <v>106783</v>
@@ -16517,16 +16498,21 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>692976</v>
+        <v>692819</v>
       </c>
       <c r="R139" t="n">
-        <v>6358428</v>
+        <v>6358429</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16590,10 +16576,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118772912</v>
+        <v>118772955</v>
       </c>
       <c r="B140" t="n">
-        <v>97882</v>
+        <v>106127</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16602,20 +16588,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219865</v>
+        <v>221849</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -16623,19 +16609,10 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16644,10 +16621,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>693227</v>
+        <v>692830</v>
       </c>
       <c r="R140" t="n">
-        <v>6358157</v>
+        <v>6358401</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16711,10 +16688,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118772935</v>
+        <v>118772938</v>
       </c>
       <c r="B141" t="n">
-        <v>97890</v>
+        <v>106783</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16723,37 +16700,28 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -16765,10 +16733,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>693002</v>
+        <v>692997</v>
       </c>
       <c r="R141" t="n">
-        <v>6358203</v>
+        <v>6358215</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16832,10 +16800,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118772938</v>
+        <v>118772939</v>
       </c>
       <c r="B142" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16848,21 +16816,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16877,10 +16845,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>692997</v>
+        <v>692971</v>
       </c>
       <c r="R142" t="n">
-        <v>6358215</v>
+        <v>6358246</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16944,10 +16912,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118772939</v>
+        <v>118773204</v>
       </c>
       <c r="B143" t="n">
-        <v>106127</v>
+        <v>57993</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16960,27 +16928,31 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -16989,13 +16961,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>692971</v>
+        <v>693184</v>
       </c>
       <c r="R143" t="n">
-        <v>6358246</v>
+        <v>6358206</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17038,7 +17010,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Betad skog, mest tall</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -17056,10 +17028,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118772962</v>
+        <v>118772942</v>
       </c>
       <c r="B144" t="n">
-        <v>106127</v>
+        <v>97828</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17068,28 +17040,37 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17101,13 +17082,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>692819</v>
+        <v>692917</v>
       </c>
       <c r="R144" t="n">
-        <v>6358429</v>
+        <v>6358307</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17168,10 +17149,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118772955</v>
+        <v>118772902</v>
       </c>
       <c r="B145" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17184,42 +17165,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>692830</v>
+        <v>693210</v>
       </c>
       <c r="R145" t="n">
-        <v>6358401</v>
+        <v>6358181</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17280,10 +17256,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118772904</v>
+        <v>118772935</v>
       </c>
       <c r="B146" t="n">
-        <v>97831</v>
+        <v>97890</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17296,21 +17272,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219798</v>
+        <v>219875</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -17325,7 +17301,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -17334,10 +17310,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693224</v>
+        <v>693002</v>
       </c>
       <c r="R146" t="n">
-        <v>6358167</v>
+        <v>6358203</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -17401,10 +17377,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118772905</v>
+        <v>118772937</v>
       </c>
       <c r="B147" t="n">
-        <v>106783</v>
+        <v>97889</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17413,38 +17389,52 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693224</v>
+        <v>693008</v>
       </c>
       <c r="R147" t="n">
-        <v>6358167</v>
+        <v>6358204</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -17508,10 +17498,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118772898</v>
+        <v>118772948</v>
       </c>
       <c r="B148" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17524,34 +17514,48 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>692998</v>
+        <v>692872</v>
       </c>
       <c r="R148" t="n">
-        <v>6358398</v>
+        <v>6358355</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -17615,10 +17619,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118773204</v>
+        <v>118772895</v>
       </c>
       <c r="B149" t="n">
-        <v>57993</v>
+        <v>108460</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17631,21 +17635,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103055</v>
+        <v>220204</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -17653,24 +17657,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>693184</v>
+        <v>692964</v>
       </c>
       <c r="R149" t="n">
-        <v>6358206</v>
+        <v>6358443</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17708,12 +17719,13 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -17731,10 +17743,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118772928</v>
+        <v>118772952</v>
       </c>
       <c r="B150" t="n">
-        <v>109962</v>
+        <v>106127</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17743,40 +17755,31 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1243</v>
+        <v>221849</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sammetsbockrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pimpinella saxifraga subsp. nigra</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Mill.) Ces.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -17785,10 +17788,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>693075</v>
+        <v>692835</v>
       </c>
       <c r="R150" t="n">
-        <v>6358190</v>
+        <v>6358377</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17852,10 +17855,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118772914</v>
+        <v>118772950</v>
       </c>
       <c r="B151" t="n">
-        <v>97855</v>
+        <v>106127</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17864,37 +17867,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219811</v>
+        <v>221849</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17906,10 +17900,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>693225</v>
+        <v>692872</v>
       </c>
       <c r="R151" t="n">
-        <v>6358156</v>
+        <v>6358355</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17973,10 +17967,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118772950</v>
+        <v>118772899</v>
       </c>
       <c r="B152" t="n">
-        <v>106127</v>
+        <v>97828</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17985,31 +17979,40 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -18018,10 +18021,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>692872</v>
+        <v>693184</v>
       </c>
       <c r="R152" t="n">
-        <v>6358355</v>
+        <v>6358206</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18085,10 +18088,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118773206</v>
+        <v>118772905</v>
       </c>
       <c r="B153" t="n">
-        <v>57993</v>
+        <v>106783</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18101,41 +18104,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103055</v>
+        <v>220079</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>693183</v>
+        <v>693224</v>
       </c>
       <c r="R153" t="n">
-        <v>6358169</v>
+        <v>6358167</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18178,7 +18177,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>Btad skog, mest tall</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18196,7 +18195,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118772961</v>
+        <v>118772946</v>
       </c>
       <c r="B154" t="n">
         <v>106127</v>
@@ -18241,10 +18240,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>692821</v>
+        <v>692894</v>
       </c>
       <c r="R154" t="n">
-        <v>6358416</v>
+        <v>6358376</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18308,7 +18307,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118772953</v>
+        <v>118772961</v>
       </c>
       <c r="B155" t="n">
         <v>106127</v>
@@ -18353,10 +18352,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>692844</v>
+        <v>692821</v>
       </c>
       <c r="R155" t="n">
-        <v>6358382</v>
+        <v>6358416</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18420,10 +18419,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118772947</v>
+        <v>118773206</v>
       </c>
       <c r="B156" t="n">
-        <v>106127</v>
+        <v>57993</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18436,27 +18435,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -18465,13 +18463,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>692900</v>
+        <v>693183</v>
       </c>
       <c r="R156" t="n">
-        <v>6358363</v>
+        <v>6358169</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18514,7 +18512,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Btad skog, mest tall</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -18532,10 +18530,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118772895</v>
+        <v>118772940</v>
       </c>
       <c r="B157" t="n">
-        <v>108460</v>
+        <v>106127</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18548,16 +18546,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220204</v>
+        <v>221849</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -18565,33 +18563,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>692964</v>
+        <v>692961</v>
       </c>
       <c r="R157" t="n">
-        <v>6358443</v>
+        <v>6358267</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18632,7 +18619,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18656,10 +18642,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118772899</v>
+        <v>118772928</v>
       </c>
       <c r="B158" t="n">
-        <v>97828</v>
+        <v>109962</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18668,30 +18654,30 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219797</v>
+        <v>1243</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Sammetsbockrot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Pimpinella saxifraga subsp. nigra</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Mill.) Ces.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18710,10 +18696,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>693184</v>
+        <v>693075</v>
       </c>
       <c r="R158" t="n">
-        <v>6358206</v>
+        <v>6358190</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18777,10 +18763,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118772902</v>
+        <v>118772904</v>
       </c>
       <c r="B159" t="n">
-        <v>106783</v>
+        <v>97831</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18789,41 +18775,55 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693210</v>
+        <v>693224</v>
       </c>
       <c r="R159" t="n">
-        <v>6358181</v>
+        <v>6358167</v>
       </c>
       <c r="S159" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -13901,7 +13901,7 @@
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY233"/>
+  <dimension ref="A1:AY240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13296,40 +13296,44 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>80741416</v>
+        <v>134684782</v>
       </c>
       <c r="B126" t="n">
-        <v>45044</v>
+        <v>43472</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>102018</v>
+        <v>101242</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -13338,23 +13342,23 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sällevägen, Gtl</t>
+          <t>Fröjel, Sälle 1:28 (8), Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>692776</v>
+        <v>692854</v>
       </c>
       <c r="R126" t="n">
-        <v>6358355</v>
+        <v>6358364</v>
       </c>
       <c r="S126" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13378,12 +13382,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2019-07-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2019-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Området är numera, efter röjningen, för ljust och öppet för dårgräsfjärilar.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13411,57 +13420,69 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>116259485</v>
+        <v>134685908</v>
       </c>
       <c r="B127" t="n">
-        <v>58636</v>
+        <v>43472</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103044</v>
+        <v>101242</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Fröjel Sälle 1:28 (8), Spangskogen., Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3), Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>692927</v>
+        <v>692881</v>
       </c>
       <c r="R127" t="n">
-        <v>6358387</v>
+        <v>6358235</v>
       </c>
       <c r="S127" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13485,12 +13506,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13499,33 +13520,29 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>Kalktallskog, delvis avverkad,tidigare betad.</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118773204</v>
+        <v>134685909</v>
       </c>
       <c r="B128" t="n">
-        <v>58676</v>
+        <v>43472</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13533,46 +13550,58 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>103055</v>
+        <v>101242</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3), Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693184</v>
+        <v>692940</v>
       </c>
       <c r="R128" t="n">
-        <v>6358206</v>
+        <v>6358296</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13596,12 +13625,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13610,13 +13639,9 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
@@ -13626,17 +13651,17 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118773206</v>
+        <v>134684770</v>
       </c>
       <c r="B129" t="n">
-        <v>58676</v>
+        <v>5497</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13644,41 +13669,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103055</v>
+        <v>101410</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Sälle 1:28 (8), Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693183</v>
+        <v>692819</v>
       </c>
       <c r="R129" t="n">
-        <v>6358169</v>
+        <v>6358410</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13702,12 +13728,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På flera tallar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13716,13 +13747,9 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>Btad skog, mest tall</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -13732,64 +13759,60 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>116259484</v>
+        <v>134684774</v>
       </c>
       <c r="B130" t="n">
-        <v>58085</v>
+        <v>5497</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>205976</v>
+        <v>101410</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fröjel Sälle 1:28 (8), Spangskogen., Gtl</t>
+          <t>Fröjel, Sälle 1:28 (8), Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>693079</v>
+        <v>693018</v>
       </c>
       <c r="R130" t="n">
-        <v>6358214</v>
+        <v>6358322</v>
       </c>
       <c r="S130" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13813,12 +13836,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>På flera tallar.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13827,71 +13855,84 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>Kalktallskog, delvis avverkad,tidigare betad.</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772926</v>
+        <v>80741416</v>
       </c>
       <c r="B131" t="n">
-        <v>111176</v>
+        <v>45044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219677</v>
+        <v>102018</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Sällevägen, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693101</v>
+        <v>692776</v>
       </c>
       <c r="R131" t="n">
-        <v>6358192</v>
+        <v>6358355</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13915,12 +13956,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2019-07-05</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2019-07-05</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13929,13 +13970,9 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall.</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
@@ -13945,17 +13982,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772899</v>
+        <v>116259485</v>
       </c>
       <c r="B132" t="n">
-        <v>99093</v>
+        <v>58636</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13963,51 +14000,46 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219797</v>
+        <v>103044</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel Sälle 1:28 (8), Spangskogen., Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693184</v>
+        <v>692927</v>
       </c>
       <c r="R132" t="n">
-        <v>6358206</v>
+        <v>6358387</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14031,12 +14063,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14050,50 +14082,50 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Kalktallskog, delvis avverkad,tidigare betad.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772916</v>
+        <v>118773204</v>
       </c>
       <c r="B133" t="n">
-        <v>99093</v>
+        <v>58676</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219797</v>
+        <v>103055</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -14101,14 +14133,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14117,13 +14144,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>693228</v>
+        <v>693184</v>
       </c>
       <c r="R133" t="n">
-        <v>6358150</v>
+        <v>6358206</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14166,7 +14193,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Betad skog, mest tall</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -14184,47 +14211,37 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118772920</v>
+        <v>118773206</v>
       </c>
       <c r="B134" t="n">
-        <v>99093</v>
+        <v>58676</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219797</v>
+        <v>103055</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -14233,13 +14250,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>693222</v>
+        <v>693183</v>
       </c>
       <c r="R134" t="n">
-        <v>6358154</v>
+        <v>6358169</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14282,7 +14299,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Btad skog, mest tall</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -14300,62 +14317,60 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118772942</v>
+        <v>134684778</v>
       </c>
       <c r="B135" t="n">
-        <v>99093</v>
+        <v>58698</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219797</v>
+        <v>103055</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Sälle 1:28 (8), Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>692917</v>
+        <v>692925</v>
       </c>
       <c r="R135" t="n">
-        <v>6358307</v>
+        <v>6358325</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14379,12 +14394,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>En sjungande i södra och en i den norra delen.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14395,11 +14415,6 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall.</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -14409,17 +14424,17 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118772904</v>
+        <v>116259484</v>
       </c>
       <c r="B136" t="n">
-        <v>99096</v>
+        <v>58085</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14427,21 +14442,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219798</v>
+        <v>205976</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -14449,29 +14464,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel Sälle 1:28 (8), Spangskogen., Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>693224</v>
+        <v>693079</v>
       </c>
       <c r="R136" t="n">
-        <v>6358167</v>
+        <v>6358214</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14495,12 +14505,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14514,28 +14524,28 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Betad skog, mest tall.</t>
+          <t>Kalktallskog, delvis avverkad,tidigare betad.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118772921</v>
+        <v>134684781</v>
       </c>
       <c r="B137" t="n">
-        <v>99096</v>
+        <v>56904</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14543,48 +14553,47 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219798</v>
+        <v>208255</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Sälle 1:28 (8), Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>693216</v>
+        <v>692854</v>
       </c>
       <c r="R137" t="n">
-        <v>6358159</v>
+        <v>6358364</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14611,12 +14620,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14625,13 +14634,9 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall.</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
@@ -14641,17 +14646,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118772922</v>
+        <v>118772926</v>
       </c>
       <c r="B138" t="n">
-        <v>99096</v>
+        <v>111176</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14659,51 +14664,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>693183</v>
+        <v>693101</v>
       </c>
       <c r="R138" t="n">
-        <v>6358169</v>
+        <v>6358192</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14764,10 +14755,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118772910</v>
+        <v>118772899</v>
       </c>
       <c r="B139" t="n">
-        <v>99103</v>
+        <v>99093</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14775,26 +14766,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219799</v>
+        <v>219797</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -14804,7 +14795,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -14813,10 +14804,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>693229</v>
+        <v>693184</v>
       </c>
       <c r="R139" t="n">
-        <v>6358152</v>
+        <v>6358206</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14849,11 +14840,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>I kanten av Sällmyr</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14885,10 +14871,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120328991</v>
+        <v>118772916</v>
       </c>
       <c r="B140" t="n">
-        <v>99103</v>
+        <v>99093</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14896,41 +14882,51 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219799</v>
+        <v>219797</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Fröjel, Sällemyr, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>693235</v>
+        <v>693228</v>
       </c>
       <c r="R140" t="n">
-        <v>6358167</v>
+        <v>6358150</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14954,12 +14950,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14968,9 +14964,13 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -14980,17 +14980,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120329359</v>
+        <v>118772920</v>
       </c>
       <c r="B141" t="n">
-        <v>99103</v>
+        <v>99093</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14998,41 +14998,51 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219799</v>
+        <v>219797</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Fröjel, Sällemyr, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>693244</v>
+        <v>693222</v>
       </c>
       <c r="R141" t="n">
-        <v>6358141</v>
+        <v>6358154</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15056,12 +15066,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15070,9 +15080,13 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -15082,17 +15096,17 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118772907</v>
+        <v>118772942</v>
       </c>
       <c r="B142" t="n">
-        <v>99120</v>
+        <v>99093</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15100,26 +15114,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219811</v>
+        <v>219797</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -15138,13 +15152,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>693224</v>
+        <v>692917</v>
       </c>
       <c r="R142" t="n">
-        <v>6358167</v>
+        <v>6358307</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15205,10 +15219,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118772914</v>
+        <v>118772904</v>
       </c>
       <c r="B143" t="n">
-        <v>99120</v>
+        <v>99096</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15216,26 +15230,26 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -15245,7 +15259,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -15254,10 +15268,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>693225</v>
+        <v>693224</v>
       </c>
       <c r="R143" t="n">
-        <v>6358156</v>
+        <v>6358167</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15321,10 +15335,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120329023</v>
+        <v>118772921</v>
       </c>
       <c r="B144" t="n">
-        <v>99120</v>
+        <v>99096</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15332,41 +15346,51 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Fröjel, Sällemyr, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>693235</v>
+        <v>693216</v>
       </c>
       <c r="R144" t="n">
-        <v>6358167</v>
+        <v>6358159</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15390,12 +15414,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15404,9 +15428,13 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -15416,17 +15444,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118772890</v>
+        <v>118772922</v>
       </c>
       <c r="B145" t="n">
-        <v>99147</v>
+        <v>99096</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15434,21 +15462,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -15463,7 +15491,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15472,13 +15500,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693044</v>
+        <v>693183</v>
       </c>
       <c r="R145" t="n">
-        <v>6358379</v>
+        <v>6358169</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15539,10 +15567,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118772912</v>
+        <v>118772910</v>
       </c>
       <c r="B146" t="n">
-        <v>99148</v>
+        <v>99103</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15550,26 +15578,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219865</v>
+        <v>219799</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -15579,7 +15607,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15588,10 +15616,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693227</v>
+        <v>693229</v>
       </c>
       <c r="R146" t="n">
-        <v>6358157</v>
+        <v>6358152</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15624,6 +15652,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>I kanten av Sällmyr</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15655,10 +15688,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118772924</v>
+        <v>120328991</v>
       </c>
       <c r="B147" t="n">
-        <v>99148</v>
+        <v>99103</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15666,51 +15699,41 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>219865</v>
+        <v>219799</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Sällemyr, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693132</v>
+        <v>693235</v>
       </c>
       <c r="R147" t="n">
         <v>6358167</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15734,12 +15757,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15748,13 +15771,9 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall.</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -15764,17 +15783,17 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118772906</v>
+        <v>120329359</v>
       </c>
       <c r="B148" t="n">
-        <v>99153</v>
+        <v>99103</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15782,51 +15801,41 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219874</v>
+        <v>219799</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Sällemyr, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693224</v>
+        <v>693244</v>
       </c>
       <c r="R148" t="n">
-        <v>6358167</v>
+        <v>6358141</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15850,12 +15859,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15864,13 +15873,9 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall.</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -15880,17 +15885,17 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118772917</v>
+        <v>118772907</v>
       </c>
       <c r="B149" t="n">
-        <v>99153</v>
+        <v>99120</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15898,26 +15903,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -15927,7 +15932,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -15936,13 +15941,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>693228</v>
+        <v>693224</v>
       </c>
       <c r="R149" t="n">
-        <v>6358150</v>
+        <v>6358167</v>
       </c>
       <c r="S149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16003,10 +16008,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118772919</v>
+        <v>118772914</v>
       </c>
       <c r="B150" t="n">
-        <v>99153</v>
+        <v>99120</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16014,26 +16019,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -16043,7 +16048,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -16052,10 +16057,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>693222</v>
+        <v>693225</v>
       </c>
       <c r="R150" t="n">
-        <v>6358154</v>
+        <v>6358156</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -16119,10 +16124,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118772935</v>
+        <v>120329023</v>
       </c>
       <c r="B151" t="n">
-        <v>99156</v>
+        <v>99120</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16130,51 +16135,41 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219875</v>
+        <v>219811</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Sällemyr, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>693002</v>
+        <v>693235</v>
       </c>
       <c r="R151" t="n">
-        <v>6358203</v>
+        <v>6358167</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16198,12 +16193,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16212,13 +16207,9 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall.</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16228,52 +16219,66 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118772896</v>
+        <v>118772890</v>
       </c>
       <c r="B152" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>692976</v>
+        <v>693044</v>
       </c>
       <c r="R152" t="n">
-        <v>6358428</v>
+        <v>6358379</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -16337,45 +16342,59 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118772900</v>
+        <v>118772912</v>
       </c>
       <c r="B153" t="n">
-        <v>108116</v>
+        <v>99148</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220079</v>
+        <v>219865</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>693224</v>
+        <v>693227</v>
       </c>
       <c r="R153" t="n">
-        <v>6358167</v>
+        <v>6358157</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16439,48 +16458,62 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118772902</v>
+        <v>118772924</v>
       </c>
       <c r="B154" t="n">
-        <v>108116</v>
+        <v>99148</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220079</v>
+        <v>219865</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>693210</v>
+        <v>693132</v>
       </c>
       <c r="R154" t="n">
-        <v>6358181</v>
+        <v>6358167</v>
       </c>
       <c r="S154" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16541,38 +16574,47 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118772915</v>
+        <v>118772906</v>
       </c>
       <c r="B155" t="n">
-        <v>108116</v>
+        <v>99153</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220079</v>
+        <v>219874</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -16581,10 +16623,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>693228</v>
+        <v>693224</v>
       </c>
       <c r="R155" t="n">
-        <v>6358150</v>
+        <v>6358167</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -16648,38 +16690,47 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118772938</v>
+        <v>118772917</v>
       </c>
       <c r="B156" t="n">
-        <v>108116</v>
+        <v>99153</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220079</v>
+        <v>219874</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -16688,13 +16739,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>692997</v>
+        <v>693228</v>
       </c>
       <c r="R156" t="n">
-        <v>6358215</v>
+        <v>6358150</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16755,37 +16806,37 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118772948</v>
+        <v>118772919</v>
       </c>
       <c r="B157" t="n">
-        <v>108116</v>
+        <v>99153</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220079</v>
+        <v>219874</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -16795,7 +16846,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -16804,10 +16855,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>692872</v>
+        <v>693222</v>
       </c>
       <c r="R157" t="n">
-        <v>6358355</v>
+        <v>6358154</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16871,38 +16922,47 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118772963</v>
+        <v>118772935</v>
       </c>
       <c r="B158" t="n">
-        <v>108116</v>
+        <v>99156</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -16911,10 +16971,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>692819</v>
+        <v>693002</v>
       </c>
       <c r="R158" t="n">
-        <v>6358429</v>
+        <v>6358203</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16978,10 +17038,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118772895</v>
+        <v>118772896</v>
       </c>
       <c r="B159" t="n">
-        <v>109815</v>
+        <v>108116</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16989,50 +17049,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220204</v>
+        <v>220079</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>692964</v>
+        <v>692976</v>
       </c>
       <c r="R159" t="n">
-        <v>6358443</v>
+        <v>6358428</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -17073,7 +17117,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -17097,10 +17140,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118772909</v>
+        <v>118772900</v>
       </c>
       <c r="B160" t="n">
-        <v>106140</v>
+        <v>108116</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17108,39 +17151,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221137</v>
+        <v>220079</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693240</v>
+        <v>693224</v>
       </c>
       <c r="R160" t="n">
-        <v>6358150</v>
+        <v>6358167</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -17173,11 +17211,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>I kanten av Sällmyr</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17209,10 +17242,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120329298</v>
+        <v>118772902</v>
       </c>
       <c r="B161" t="n">
-        <v>106140</v>
+        <v>108116</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17220,41 +17253,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221137</v>
+        <v>220079</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Fröjel, Sällemyr, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693244</v>
+        <v>693210</v>
       </c>
       <c r="R161" t="n">
-        <v>6358141</v>
+        <v>6358181</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17278,12 +17307,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17292,9 +17321,13 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
@@ -17304,17 +17337,17 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>118772894</v>
+        <v>118772915</v>
       </c>
       <c r="B162" t="n">
-        <v>107517</v>
+        <v>108116</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17322,27 +17355,27 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -17351,10 +17384,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>692895</v>
+        <v>693228</v>
       </c>
       <c r="R162" t="n">
-        <v>6358525</v>
+        <v>6358150</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17418,10 +17451,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>118772898</v>
+        <v>118772938</v>
       </c>
       <c r="B163" t="n">
-        <v>107517</v>
+        <v>108116</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17429,34 +17462,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>692998</v>
+        <v>692997</v>
       </c>
       <c r="R163" t="n">
-        <v>6358398</v>
+        <v>6358215</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17520,10 +17558,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>118772939</v>
+        <v>118772948</v>
       </c>
       <c r="B164" t="n">
-        <v>107517</v>
+        <v>108116</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17531,24 +17569,33 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17560,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>692971</v>
+        <v>692872</v>
       </c>
       <c r="R164" t="n">
-        <v>6358246</v>
+        <v>6358355</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17627,10 +17674,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>118772940</v>
+        <v>118772963</v>
       </c>
       <c r="B165" t="n">
-        <v>107517</v>
+        <v>108116</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17638,27 +17685,27 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -17667,10 +17714,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>692961</v>
+        <v>692819</v>
       </c>
       <c r="R165" t="n">
-        <v>6358267</v>
+        <v>6358429</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -17734,10 +17781,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>118772941</v>
+        <v>118772895</v>
       </c>
       <c r="B166" t="n">
-        <v>107517</v>
+        <v>109815</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17745,16 +17792,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -17762,22 +17809,33 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Spangskogen Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>692930</v>
+        <v>692964</v>
       </c>
       <c r="R166" t="n">
-        <v>6358283</v>
+        <v>6358443</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -17818,6 +17876,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -17841,10 +17900,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118772945</v>
+        <v>118772909</v>
       </c>
       <c r="B167" t="n">
-        <v>107517</v>
+        <v>106140</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17852,16 +17911,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221849</v>
+        <v>221137</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -17872,7 +17931,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -17881,10 +17940,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>692922</v>
+        <v>693240</v>
       </c>
       <c r="R167" t="n">
-        <v>6358382</v>
+        <v>6358150</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -17921,7 +17980,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Spridd i hela skiftet.</t>
+          <t>I kanten av Sällmyr</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17953,10 +18012,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>118772946</v>
+        <v>120329298</v>
       </c>
       <c r="B168" t="n">
-        <v>107517</v>
+        <v>106140</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17964,16 +18023,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221849</v>
+        <v>221137</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -17982,24 +18041,23 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
+          <t>Fröjel, Sällemyr, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>692894</v>
+        <v>693244</v>
       </c>
       <c r="R168" t="n">
-        <v>6358376</v>
+        <v>6358141</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18023,12 +18081,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18037,13 +18095,9 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>Betad skog, mest tall.</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -18053,14 +18107,14 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>118772947</v>
+        <v>118772894</v>
       </c>
       <c r="B169" t="n">
         <v>107517</v>
@@ -18100,10 +18154,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>692900</v>
+        <v>692895</v>
       </c>
       <c r="R169" t="n">
-        <v>6358363</v>
+        <v>6358525</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -18167,7 +18221,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118772950</v>
+        <v>118772898</v>
       </c>
       <c r="B170" t="n">
         <v>107517</v>
@@ -18196,21 +18250,16 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>692872</v>
+        <v>692998</v>
       </c>
       <c r="R170" t="n">
-        <v>6358355</v>
+        <v>6358398</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18274,7 +18323,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118772952</v>
+        <v>118772939</v>
       </c>
       <c r="B171" t="n">
         <v>107517</v>
@@ -18314,10 +18363,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>692835</v>
+        <v>692971</v>
       </c>
       <c r="R171" t="n">
-        <v>6358377</v>
+        <v>6358246</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18381,7 +18430,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>118772953</v>
+        <v>118772940</v>
       </c>
       <c r="B172" t="n">
         <v>107517</v>
@@ -18421,10 +18470,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>692844</v>
+        <v>692961</v>
       </c>
       <c r="R172" t="n">
-        <v>6358382</v>
+        <v>6358267</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18488,7 +18537,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>118772954</v>
+        <v>118772941</v>
       </c>
       <c r="B173" t="n">
         <v>107517</v>
@@ -18528,10 +18577,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>692826</v>
+        <v>692930</v>
       </c>
       <c r="R173" t="n">
-        <v>6358398</v>
+        <v>6358283</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -18595,7 +18644,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>118772955</v>
+        <v>118772945</v>
       </c>
       <c r="B174" t="n">
         <v>107517</v>
@@ -18635,10 +18684,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>692830</v>
+        <v>692922</v>
       </c>
       <c r="R174" t="n">
-        <v>6358401</v>
+        <v>6358382</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18671,6 +18720,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Spridd i hela skiftet.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18702,7 +18756,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>118772961</v>
+        <v>118772946</v>
       </c>
       <c r="B175" t="n">
         <v>107517</v>
@@ -18742,10 +18796,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>692821</v>
+        <v>692894</v>
       </c>
       <c r="R175" t="n">
-        <v>6358416</v>
+        <v>6358376</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18809,7 +18863,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>118772962</v>
+        <v>118772947</v>
       </c>
       <c r="B176" t="n">
         <v>107517</v>
@@ -18849,10 +18903,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>692819</v>
+        <v>692900</v>
       </c>
       <c r="R176" t="n">
-        <v>6358429</v>
+        <v>6358363</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18916,7 +18970,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>118772964</v>
+        <v>118772950</v>
       </c>
       <c r="B177" t="n">
         <v>107517</v>
@@ -18956,13 +19010,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>692813</v>
+        <v>692872</v>
       </c>
       <c r="R177" t="n">
-        <v>6358438</v>
+        <v>6358355</v>
       </c>
       <c r="S177" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19023,45 +19077,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>116259075</v>
+        <v>118772952</v>
       </c>
       <c r="B178" t="n">
-        <v>101326</v>
+        <v>107517</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Fröjel Sälle 1:28 (8), Spangskogen., Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>692862</v>
+        <v>692835</v>
       </c>
       <c r="R178" t="n">
-        <v>6358454</v>
+        <v>6358377</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -19088,17 +19147,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Spridd hela skiftet.</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19112,62 +19166,53 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>Kalktallskog, delvis avverkad,tidigare betad.</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118772937</v>
+        <v>118772953</v>
       </c>
       <c r="B179" t="n">
-        <v>99155</v>
+        <v>107517</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>223621</v>
+        <v>221849</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -19179,10 +19224,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>693008</v>
+        <v>692844</v>
       </c>
       <c r="R179" t="n">
-        <v>6358204</v>
+        <v>6358382</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19246,52 +19291,53 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120328999</v>
+        <v>118772954</v>
       </c>
       <c r="B180" t="n">
-        <v>99155</v>
+        <v>107517</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>223621</v>
+        <v>221849</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Fröjel, Sällemyr, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>693235</v>
+        <v>692826</v>
       </c>
       <c r="R180" t="n">
-        <v>6358167</v>
+        <v>6358398</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19315,12 +19361,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19329,9 +19375,13 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
@@ -19341,55 +19391,60 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>96973998</v>
+        <v>118772955</v>
       </c>
       <c r="B181" t="n">
-        <v>86727</v>
+        <v>107517</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>239064</v>
+        <v>221849</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pärlchampinjon</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Agaricus moelleri</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Wasser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>693078</v>
+        <v>692830</v>
       </c>
       <c r="R181" t="n">
-        <v>6358313</v>
+        <v>6358401</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19413,12 +19468,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19429,67 +19484,74 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>112772705</v>
+        <v>118772961</v>
       </c>
       <c r="B182" t="n">
-        <v>90665</v>
+        <v>107517</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>245042</v>
+        <v>221849</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Tommys hägn, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>692960</v>
+        <v>692821</v>
       </c>
       <c r="R182" t="n">
-        <v>6358369</v>
+        <v>6358416</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19513,12 +19575,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19527,71 +19589,76 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY182" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>112772722</v>
+        <v>118772962</v>
       </c>
       <c r="B183" t="n">
-        <v>90665</v>
+        <v>107517</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>245042</v>
+        <v>221849</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>692961</v>
+        <v>692819</v>
       </c>
       <c r="R183" t="n">
-        <v>6358384</v>
+        <v>6358429</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19615,12 +19682,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19631,68 +19698,74 @@
       </c>
       <c r="AG183" t="b">
         <v>0</v>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY183" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>69286345</v>
+        <v>118772964</v>
       </c>
       <c r="B184" t="n">
-        <v>87291</v>
+        <v>107517</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>248955</v>
+        <v>221849</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>693162</v>
+        <v>692813</v>
       </c>
       <c r="R184" t="n">
-        <v>6358207</v>
+        <v>6358438</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19716,12 +19789,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19735,66 +19808,66 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+          <t>Betad skog, mest tall.</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>69286351</v>
+        <v>116259075</v>
       </c>
       <c r="B185" t="n">
-        <v>87291</v>
+        <v>101326</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>248955</v>
+        <v>222498</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel Sälle 1:28 (8), Spangskogen., Gtl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>693097</v>
+        <v>692862</v>
       </c>
       <c r="R185" t="n">
-        <v>6358275</v>
+        <v>6358454</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19818,12 +19891,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Spridd hela skiftet.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19837,66 +19915,80 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+          <t>Kalktallskog, delvis avverkad,tidigare betad.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>96964013</v>
+        <v>118772937</v>
       </c>
       <c r="B186" t="n">
-        <v>87291</v>
+        <v>99155</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>248955</v>
+        <v>223621</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Spangskogen, Fröjel Sälle 1:28, Gtl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>692893</v>
+        <v>693008</v>
       </c>
       <c r="R186" t="n">
-        <v>6358447</v>
+        <v>6358204</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19920,12 +20012,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19936,61 +20028,70 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>Betad skog, mest tall.</t>
+        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>96974020</v>
+        <v>120328999</v>
       </c>
       <c r="B187" t="n">
-        <v>87291</v>
+        <v>99155</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>248955</v>
+        <v>223621</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Sällemyr, Gtl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>692828</v>
+        <v>693235</v>
       </c>
       <c r="R187" t="n">
-        <v>6358430</v>
+        <v>6358167</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20017,12 +20118,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20031,66 +20132,64 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>104120203</v>
+        <v>96973998</v>
       </c>
       <c r="B188" t="n">
-        <v>87291</v>
+        <v>86727</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>248955</v>
+        <v>239064</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Pärlchampinjon</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Agaricus moelleri</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Wasser</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>692818</v>
+        <v>693078</v>
       </c>
       <c r="R188" t="n">
-        <v>6358461</v>
+        <v>6358313</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20117,12 +20216,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20131,71 +20230,69 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY188" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>104281159</v>
+        <v>112772705</v>
       </c>
       <c r="B189" t="n">
-        <v>87291</v>
+        <v>90665</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>248955</v>
+        <v>245042</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve OSO, Gtl</t>
+          <t>Tommys hägn, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>692876</v>
+        <v>692960</v>
       </c>
       <c r="R189" t="n">
-        <v>6358358</v>
+        <v>6358369</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20219,12 +20316,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20233,76 +20330,68 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>6625223</v>
+        <v>112772722</v>
       </c>
       <c r="B190" t="n">
-        <v>87262</v>
+        <v>90665</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Fröjel, Sälle, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>692936</v>
+        <v>692961</v>
       </c>
       <c r="R190" t="n">
-        <v>6358461</v>
+        <v>6358384</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20329,12 +20418,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2011-10-11</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2011-10-11</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20349,22 +20438,26 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
-        </is>
-      </c>
-      <c r="AY190" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>6625224</v>
+        <v>69286345</v>
       </c>
       <c r="B191" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20372,43 +20465,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Fröjel, Sälle, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>692802</v>
+        <v>693162</v>
       </c>
       <c r="R191" t="n">
-        <v>6358389</v>
+        <v>6358207</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20435,12 +20519,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2011-10-11</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2011-10-11</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20451,26 +20535,31 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>69286339</v>
+        <v>69286351</v>
       </c>
       <c r="B192" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20478,21 +20567,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20502,10 +20591,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>692983</v>
+        <v>693097</v>
       </c>
       <c r="R192" t="n">
-        <v>6358433</v>
+        <v>6358275</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20569,10 +20658,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>69286344</v>
+        <v>96964013</v>
       </c>
       <c r="B193" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20580,34 +20669,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>693162</v>
+        <v>692893</v>
       </c>
       <c r="R193" t="n">
-        <v>6358207</v>
+        <v>6358447</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20634,12 +20723,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20650,31 +20739,26 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>69286352</v>
+        <v>96974020</v>
       </c>
       <c r="B194" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20682,34 +20766,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>693097</v>
+        <v>692828</v>
       </c>
       <c r="R194" t="n">
-        <v>6358275</v>
+        <v>6358430</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20736,12 +20820,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20752,31 +20836,26 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Helena Björnström, Michael Krikorev</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>69286362</v>
+        <v>104120203</v>
       </c>
       <c r="B195" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20784,34 +20863,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>692902</v>
+        <v>692818</v>
       </c>
       <c r="R195" t="n">
-        <v>6358419</v>
+        <v>6358461</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20838,12 +20920,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20852,33 +20934,33 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
-        </is>
-      </c>
-      <c r="AY195" t="inlineStr"/>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>69286367</v>
+        <v>104281159</v>
       </c>
       <c r="B196" t="n">
-        <v>87262</v>
+        <v>87291</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20886,34 +20968,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel, Sigdarve OSO, Gtl</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>692873</v>
+        <v>692876</v>
       </c>
       <c r="R196" t="n">
-        <v>6358482</v>
+        <v>6358358</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20940,12 +21022,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20956,28 +21038,27 @@
       </c>
       <c r="AG196" t="b">
         <v>0</v>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
-        </is>
-      </c>
-      <c r="AY196" t="inlineStr"/>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>69286369</v>
+        <v>6625223</v>
       </c>
       <c r="B197" t="n">
         <v>87262</v>
@@ -21005,17 +21086,26 @@
           <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel, Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>692850</v>
+        <v>692936</v>
       </c>
       <c r="R197" t="n">
-        <v>6358492</v>
+        <v>6358461</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21042,12 +21132,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2011-10-11</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2011-10-11</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21058,28 +21148,23 @@
       </c>
       <c r="AG197" t="b">
         <v>0</v>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>96963991</v>
+        <v>6625224</v>
       </c>
       <c r="B198" t="n">
         <v>87262</v>
@@ -21107,17 +21192,26 @@
           <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Fröjel, Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>692913</v>
+        <v>692802</v>
       </c>
       <c r="R198" t="n">
-        <v>6358415</v>
+        <v>6358389</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21144,12 +21238,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2011-10-11</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2011-10-11</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21164,19 +21258,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>96974001</v>
+        <v>69286339</v>
       </c>
       <c r="B199" t="n">
         <v>87262</v>
@@ -21207,14 +21301,14 @@
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>692888</v>
+        <v>692983</v>
       </c>
       <c r="R199" t="n">
-        <v>6358413</v>
+        <v>6358433</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21241,12 +21335,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21257,23 +21351,28 @@
       </c>
       <c r="AG199" t="b">
         <v>0</v>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>96974002</v>
+        <v>69286344</v>
       </c>
       <c r="B200" t="n">
         <v>87262</v>
@@ -21304,14 +21403,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>692907</v>
+        <v>693162</v>
       </c>
       <c r="R200" t="n">
-        <v>6358405</v>
+        <v>6358207</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21338,12 +21437,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21354,23 +21453,28 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>96974003</v>
+        <v>69286352</v>
       </c>
       <c r="B201" t="n">
         <v>87262</v>
@@ -21401,14 +21505,14 @@
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>692828</v>
+        <v>693097</v>
       </c>
       <c r="R201" t="n">
-        <v>6358430</v>
+        <v>6358275</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21435,12 +21539,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21451,23 +21555,28 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>104112255</v>
+        <v>69286362</v>
       </c>
       <c r="B202" t="n">
         <v>87262</v>
@@ -21496,20 +21605,19 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gotland, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>692802</v>
+        <v>692902</v>
       </c>
       <c r="R202" t="n">
-        <v>6358403</v>
+        <v>6358419</v>
       </c>
       <c r="S202" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21533,12 +21641,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21549,23 +21657,28 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>104120253</v>
+        <v>69286367</v>
       </c>
       <c r="B203" t="n">
         <v>87262</v>
@@ -21594,19 +21707,16 @@
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>692826</v>
+        <v>692873</v>
       </c>
       <c r="R203" t="n">
-        <v>6358375</v>
+        <v>6358482</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21633,12 +21743,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21647,30 +21757,30 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY203" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>104120255</v>
+        <v>69286369</v>
       </c>
       <c r="B204" t="n">
         <v>87262</v>
@@ -21699,19 +21809,16 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>692825</v>
+        <v>692850</v>
       </c>
       <c r="R204" t="n">
-        <v>6358389</v>
+        <v>6358492</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21738,12 +21845,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21752,30 +21859,30 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY204" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>104120256</v>
+        <v>96963991</v>
       </c>
       <c r="B205" t="n">
         <v>87262</v>
@@ -21804,19 +21911,16 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>692814</v>
+        <v>692913</v>
       </c>
       <c r="R205" t="n">
-        <v>6358403</v>
+        <v>6358415</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21843,12 +21947,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21857,30 +21961,25 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY205" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>104120257</v>
+        <v>96974001</v>
       </c>
       <c r="B206" t="n">
         <v>87262</v>
@@ -21909,19 +22008,16 @@
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>692835</v>
+        <v>692888</v>
       </c>
       <c r="R206" t="n">
-        <v>6358445</v>
+        <v>6358413</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21948,12 +22044,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21962,30 +22058,25 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY206" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>104120258</v>
+        <v>96974002</v>
       </c>
       <c r="B207" t="n">
         <v>87262</v>
@@ -22014,19 +22105,16 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>692859</v>
+        <v>692907</v>
       </c>
       <c r="R207" t="n">
-        <v>6358485</v>
+        <v>6358405</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22053,12 +22141,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22067,30 +22155,25 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY207" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>104120259</v>
+        <v>96974003</v>
       </c>
       <c r="B208" t="n">
         <v>87262</v>
@@ -22119,19 +22202,16 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>692897</v>
+        <v>692828</v>
       </c>
       <c r="R208" t="n">
-        <v>6358528</v>
+        <v>6358430</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22158,12 +22238,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22172,30 +22252,25 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>104179750</v>
+        <v>104112255</v>
       </c>
       <c r="B209" t="n">
         <v>87262</v>
@@ -22224,19 +22299,20 @@
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Tommys barränge + Fröjel-Sigdarve, Gtl</t>
+          <t>Fröjel Sälle, Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>692757</v>
+        <v>692802</v>
       </c>
       <c r="R209" t="n">
-        <v>6358401</v>
+        <v>6358403</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22280,23 +22356,19 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY209" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>104281160</v>
+        <v>104120253</v>
       </c>
       <c r="B210" t="n">
         <v>87262</v>
@@ -22325,16 +22397,19 @@
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve OSO, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>692878</v>
+        <v>692826</v>
       </c>
       <c r="R210" t="n">
-        <v>6358352</v>
+        <v>6358375</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22375,67 +22450,71 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>104120280</v>
+        <v>104120255</v>
       </c>
       <c r="B211" t="n">
-        <v>87323</v>
+        <v>87262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>249228</v>
+        <v>248956</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>692864</v>
+        <v>692825</v>
       </c>
       <c r="R211" t="n">
-        <v>6358490</v>
+        <v>6358389</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22476,6 +22555,7 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -22487,7 +22567,7 @@
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -22498,45 +22578,48 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>69286353</v>
+        <v>104120256</v>
       </c>
       <c r="B212" t="n">
-        <v>87225</v>
+        <v>87262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>249248</v>
+        <v>248956</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blek bananspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cortinarius citrino-olivaceus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>693097</v>
+        <v>692814</v>
       </c>
       <c r="R212" t="n">
-        <v>6358275</v>
+        <v>6358403</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22563,12 +22646,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22577,33 +22660,33 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
-        </is>
-      </c>
-      <c r="AY212" t="inlineStr"/>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>104120204</v>
+        <v>104120257</v>
       </c>
       <c r="B213" t="n">
-        <v>90707</v>
+        <v>87262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22611,34 +22694,37 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>249376</v>
+        <v>248956</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullmusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Tricholoma squarrulosum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Bres.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>692898</v>
+        <v>692835</v>
       </c>
       <c r="R213" t="n">
-        <v>6358514</v>
+        <v>6358445</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22702,10 +22788,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>104281156</v>
+        <v>104120258</v>
       </c>
       <c r="B214" t="n">
-        <v>90707</v>
+        <v>87262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22713,34 +22799,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>249376</v>
+        <v>248956</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ullmusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Tricholoma squarrulosum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Bres.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve OSO, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>692895</v>
+        <v>692859</v>
       </c>
       <c r="R214" t="n">
-        <v>6358516</v>
+        <v>6358485</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22788,61 +22877,64 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>69286347</v>
+        <v>104120259</v>
       </c>
       <c r="B215" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>693162</v>
+        <v>692897</v>
       </c>
       <c r="R215" t="n">
-        <v>6358207</v>
+        <v>6358528</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22869,12 +22961,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22883,68 +22975,68 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
-        </is>
-      </c>
-      <c r="AY215" t="inlineStr"/>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>69286371</v>
+        <v>104179750</v>
       </c>
       <c r="B216" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
+          <t>Tommys barränge + Fröjel-Sigdarve, Gtl</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>692850</v>
+        <v>692757</v>
       </c>
       <c r="R216" t="n">
-        <v>6358492</v>
+        <v>6358401</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22971,12 +23063,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2015-10-12</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -22987,70 +23079,68 @@
       </c>
       <c r="AG216" t="b">
         <v>0</v>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
-        </is>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
-        </is>
-      </c>
-      <c r="AY216" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>104112257</v>
+        <v>104281160</v>
       </c>
       <c r="B217" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gotland, Gtl</t>
+          <t>Fröjel, Sigdarve OSO, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>692802</v>
+        <v>692878</v>
       </c>
       <c r="R217" t="n">
-        <v>6358403</v>
+        <v>6358352</v>
       </c>
       <c r="S217" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23094,22 +23184,26 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY217" t="inlineStr"/>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>104120231</v>
+        <v>104120280</v>
       </c>
       <c r="B218" t="n">
-        <v>87346</v>
+        <v>87323</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23117,37 +23211,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6003295</v>
+        <v>249228</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>692861</v>
+        <v>692864</v>
       </c>
       <c r="R218" t="n">
-        <v>6358486</v>
+        <v>6358490</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23188,7 +23279,6 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -23200,7 +23290,7 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Laritza Pettersson, Niklas Johansson, Brian Johnson, Cecilia Nygren</t>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -23211,27 +23301,27 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>112725819</v>
+        <v>69286353</v>
       </c>
       <c r="B219" t="n">
-        <v>87346</v>
+        <v>87225</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6003295</v>
+        <v>249248</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blek bananspindling</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius citrino-olivaceus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -23242,14 +23332,14 @@
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>692911</v>
+        <v>693097</v>
       </c>
       <c r="R219" t="n">
-        <v>6358452</v>
+        <v>6358275</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23276,12 +23366,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23292,68 +23382,66 @@
       </c>
       <c r="AG219" t="b">
         <v>0</v>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY219" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>112725866</v>
+        <v>104120204</v>
       </c>
       <c r="B220" t="n">
-        <v>87346</v>
+        <v>90707</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6003295</v>
+        <v>249376</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ullmusseron</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma squarrulosum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>692923</v>
+        <v>692898</v>
       </c>
       <c r="R220" t="n">
-        <v>6358440</v>
+        <v>6358514</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23380,12 +23468,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23406,56 +23494,56 @@
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna Gotland</t>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>113015019</v>
+        <v>104281156</v>
       </c>
       <c r="B221" t="n">
-        <v>87346</v>
+        <v>90707</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6003295</v>
+        <v>249376</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ullmusseron</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma squarrulosum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel, Sigdarve OSO, Gtl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>692903</v>
+        <v>692895</v>
       </c>
       <c r="R221" t="n">
-        <v>6358421</v>
+        <v>6358516</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23482,12 +23570,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23496,6 +23584,7 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -23512,16 +23601,16 @@
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna Gotland</t>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>96964007</v>
+        <v>69286347</v>
       </c>
       <c r="B222" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23529,34 +23618,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>692916</v>
+        <v>693162</v>
       </c>
       <c r="R222" t="n">
-        <v>6358429</v>
+        <v>6358207</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23583,12 +23672,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23599,26 +23688,31 @@
       </c>
       <c r="AG222" t="b">
         <v>0</v>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>96964008</v>
+        <v>69286371</v>
       </c>
       <c r="B223" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23626,34 +23720,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Fröjel, Sigdarve, Sälle N., Gtl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>692896</v>
+        <v>692850</v>
       </c>
       <c r="R223" t="n">
-        <v>6358444</v>
+        <v>6358492</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23680,12 +23774,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23696,26 +23790,31 @@
       </c>
       <c r="AG223" t="b">
         <v>0</v>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>ängstallskog; kontinuitetsskog; skogsbete</t>
+        </is>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>96964009</v>
+        <v>104112257</v>
       </c>
       <c r="B224" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23723,37 +23822,38 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Fröjel Sälle, Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>692900</v>
+        <v>692802</v>
       </c>
       <c r="R224" t="n">
-        <v>6358467</v>
+        <v>6358403</v>
       </c>
       <c r="S224" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -23777,12 +23877,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23797,22 +23897,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>96974011</v>
+        <v>104120231</v>
       </c>
       <c r="B225" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23820,34 +23920,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>693101</v>
+        <v>692861</v>
       </c>
       <c r="R225" t="n">
-        <v>6358288</v>
+        <v>6358486</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23874,12 +23977,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23888,28 +23991,33 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY225" t="inlineStr"/>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Laritza Pettersson, Niklas Johansson, Brian Johnson, Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>96974012</v>
+        <v>112725819</v>
       </c>
       <c r="B226" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23917,34 +24025,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>692812</v>
+        <v>692911</v>
       </c>
       <c r="R226" t="n">
-        <v>6358398</v>
+        <v>6358452</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23971,12 +24079,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23991,22 +24099,26 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY226" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>96974013</v>
+        <v>112725866</v>
       </c>
       <c r="B227" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24014,34 +24126,37 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>692787</v>
+        <v>692923</v>
       </c>
       <c r="R227" t="n">
-        <v>6358419</v>
+        <v>6358440</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24068,12 +24183,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24082,28 +24197,33 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY227" t="inlineStr"/>
+          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>96974014</v>
+        <v>113015019</v>
       </c>
       <c r="B228" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24111,34 +24231,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>692887</v>
+        <v>692903</v>
       </c>
       <c r="R228" t="n">
-        <v>6358511</v>
+        <v>6358421</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24165,12 +24285,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24185,19 +24305,23 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Helena Björnström, Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY228" t="inlineStr"/>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>104112847</v>
+        <v>96964007</v>
       </c>
       <c r="B229" t="n">
         <v>87312</v>
@@ -24226,20 +24350,19 @@
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>692884</v>
+        <v>692916</v>
       </c>
       <c r="R229" t="n">
-        <v>6358436</v>
+        <v>6358429</v>
       </c>
       <c r="S229" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -24263,22 +24386,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>10:01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>10:01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24293,19 +24406,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>104120272</v>
+        <v>96964008</v>
       </c>
       <c r="B230" t="n">
         <v>87312</v>
@@ -24336,14 +24449,14 @@
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>692885</v>
+        <v>692896</v>
       </c>
       <c r="R230" t="n">
-        <v>6358368</v>
+        <v>6358444</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24370,12 +24483,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24384,30 +24497,25 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
-      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
-        </is>
-      </c>
-      <c r="AY230" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>104120274</v>
+        <v>96964009</v>
       </c>
       <c r="B231" t="n">
         <v>87312</v>
@@ -24438,14 +24546,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>692808</v>
+        <v>692900</v>
       </c>
       <c r="R231" t="n">
-        <v>6358405</v>
+        <v>6358467</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24472,12 +24580,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24486,30 +24594,25 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
-        </is>
-      </c>
-      <c r="AY231" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>104120276</v>
+        <v>96974011</v>
       </c>
       <c r="B232" t="n">
         <v>87312</v>
@@ -24540,14 +24643,14 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>692831</v>
+        <v>693101</v>
       </c>
       <c r="R232" t="n">
-        <v>6358446</v>
+        <v>6358288</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24574,12 +24677,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24588,74 +24691,66 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
-      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
-        </is>
-      </c>
-      <c r="AY232" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120369935</v>
+        <v>96974012</v>
       </c>
       <c r="B233" t="n">
-        <v>87374</v>
+        <v>87312</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6052416</v>
+        <v>6037417</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Tommys barränge, Gtl</t>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>692889</v>
+        <v>692812</v>
       </c>
       <c r="R233" t="n">
-        <v>6358353</v>
+        <v>6358398</v>
       </c>
       <c r="S233" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24679,12 +24774,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24693,22 +24788,730 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
-      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>96974013</v>
+      </c>
+      <c r="B234" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>692787</v>
+      </c>
+      <c r="R234" t="n">
+        <v>6358419</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>96974014</v>
+      </c>
+      <c r="B235" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Fröjel Ö, Tommys barränge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>692887</v>
+      </c>
+      <c r="R235" t="n">
+        <v>6358511</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>104112847</v>
+      </c>
+      <c r="B236" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>692884</v>
+      </c>
+      <c r="R236" t="n">
+        <v>6358436</v>
+      </c>
+      <c r="S236" t="n">
+        <v>25</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>104120272</v>
+      </c>
+      <c r="B237" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>692885</v>
+      </c>
+      <c r="R237" t="n">
+        <v>6358368</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>104120274</v>
+      </c>
+      <c r="B238" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>692808</v>
+      </c>
+      <c r="R238" t="n">
+        <v>6358405</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF238" t="inlineStr"/>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>104120276</v>
+      </c>
+      <c r="B239" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>692831</v>
+      </c>
+      <c r="R239" t="n">
+        <v>6358446</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Brian Johnson, Laritza Pettersson, Niklas Johansson, Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>120369935</v>
+      </c>
+      <c r="B240" t="n">
+        <v>87374</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Tommys barränge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>692889</v>
+      </c>
+      <c r="R240" t="n">
+        <v>6358353</v>
+      </c>
+      <c r="S240" t="n">
+        <v>25</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF240" t="inlineStr"/>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
           <t>Ossian Rydebjörk</t>
         </is>
       </c>
-      <c r="AX233" t="inlineStr">
+      <c r="AX240" t="inlineStr">
         <is>
           <t>Ossian Rydebjörk</t>
         </is>
       </c>
-      <c r="AY233" t="inlineStr"/>
+      <c r="AY240" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4716-2024 artfynd.xlsx
+++ b/artfynd/A 4716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY240"/>
+  <dimension ref="A1:AZ240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/171691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286354</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286350</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772928</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1088128</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973986</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286349</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974007</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974008</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286357</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,6 +2167,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286346</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1487385</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73363262</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973989</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116259481</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2643,6 +2738,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685908</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2762,6 +2862,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685909</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2873,6 +2978,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118773204</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2979,6 +3089,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118773206</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3090,6 +3205,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116259484</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3192,6 +3312,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772926</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3308,6 +3433,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772899</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3424,6 +3554,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772916</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3540,6 +3675,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772920</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3656,6 +3796,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772942</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3772,6 +3917,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772904</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3888,6 +4038,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772921</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4004,6 +4159,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772922</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4125,6 +4285,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772910</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4227,6 +4392,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120328991</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4329,6 +4499,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120329359</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4445,6 +4620,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772907</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4561,6 +4741,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772914</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4663,6 +4848,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120329023</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4779,6 +4969,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772912</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4895,6 +5090,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772924</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5011,6 +5211,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772906</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5127,6 +5332,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772917</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5243,6 +5453,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772919</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5359,6 +5574,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772935</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5461,6 +5681,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772900</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5563,6 +5788,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772902</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5670,6 +5900,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772915</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5777,6 +6012,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772938</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5889,6 +6129,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772909</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5991,6 +6236,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120329298</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6098,6 +6348,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772939</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6205,6 +6460,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772940</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6312,6 +6572,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772941</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6428,6 +6693,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772937</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6530,6 +6800,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120328999</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6632,6 +6907,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286345</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6734,6 +7014,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286351</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6836,6 +7121,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286344</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6938,6 +7228,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286352</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7040,6 +7335,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286353</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7142,6 +7442,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286347</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7239,6 +7544,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974011</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7336,6 +7646,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974005</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7437,6 +7752,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120269</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7538,6 +7858,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120270</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7639,6 +7964,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179753</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7740,6 +8070,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179754</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7841,6 +8176,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179755</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7942,6 +8282,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725830</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8043,6 +8388,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015023</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8140,6 +8490,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974024</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8237,6 +8592,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8334,6 +8694,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974026</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8432,6 +8797,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112260</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8540,6 +8910,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112683</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8657,6 +9032,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104114203</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8758,6 +9138,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120288</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8859,6 +9244,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120290</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8960,6 +9350,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120292</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9061,6 +9456,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120293</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9162,6 +9562,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120294</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9263,6 +9668,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120295</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9364,6 +9774,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120296</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9465,6 +9880,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120297</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9566,6 +9986,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179740</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9667,6 +10092,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179741</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9768,6 +10198,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104281161</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9870,6 +10305,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/171688</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9972,6 +10412,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/171689</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10074,6 +10519,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/171690</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10172,6 +10622,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286359</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10279,6 +10734,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112348</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10376,6 +10836,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120265</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10483,6 +10948,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/174692</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10580,6 +11050,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974006</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10685,6 +11160,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120223</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10791,6 +11271,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/145575</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10898,6 +11383,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772893</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11004,6 +11494,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/447806</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11101,6 +11596,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96963984</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11202,6 +11702,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179747</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11308,6 +11813,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1088129</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11405,6 +11915,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973987</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11502,6 +12017,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973988</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11600,6 +12120,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104113390</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11705,6 +12230,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120198</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11810,6 +12340,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120199</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11909,6 +12444,11 @@
       <c r="AY108" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179735</t>
         </is>
       </c>
     </row>
@@ -12016,6 +12556,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772704</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12121,6 +12666,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120263</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12218,6 +12768,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973995</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12323,6 +12878,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120214</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12424,6 +12984,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015015</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12521,6 +13086,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1160805</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12626,6 +13196,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120213</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12727,6 +13302,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179751</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12829,6 +13409,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286341</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12931,6 +13516,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286365</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13033,6 +13623,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286368</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13130,6 +13725,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96964003</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13227,6 +13827,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96964004</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13324,6 +13929,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96964005</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13421,6 +14031,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974009</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13518,6 +14133,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974010</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13623,6 +14243,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120234</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13728,6 +14353,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120235</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13833,6 +14463,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120236</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13938,6 +14573,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120237</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14043,6 +14683,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120239</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14148,6 +14793,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120240</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14249,6 +14899,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179746</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14350,6 +15005,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015024</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14451,6 +15111,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015025</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14544,6 +15209,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1208304</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14642,6 +15312,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286358</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14739,6 +15414,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1356625</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14841,6 +15521,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286340</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14943,6 +15628,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286361</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15045,6 +15735,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286364</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15146,6 +15841,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179760</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15243,6 +15943,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1755349</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15345,6 +16050,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286370</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15442,6 +16152,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973999</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15547,6 +16262,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120225</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15652,6 +16372,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120226</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15757,6 +16482,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120227</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15862,6 +16592,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120228</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15967,6 +16702,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120229</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16068,6 +16808,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015014</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16170,6 +16915,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286366</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16271,6 +17021,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120268</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16372,6 +17127,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179752</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16473,6 +17233,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120271</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16574,6 +17339,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179756</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16680,6 +17450,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1487386</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16777,6 +17552,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973990</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16874,6 +17654,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973991</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16971,6 +17756,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973992</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17068,6 +17858,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973993</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17176,6 +17971,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112678</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17292,6 +18092,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104114630</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17397,6 +18202,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120206</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17496,6 +18306,11 @@
       <c r="AY163" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179736</t>
         </is>
       </c>
     </row>
@@ -17603,6 +18418,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772706</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17700,6 +18520,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974000</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17798,6 +18623,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104113400</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17903,6 +18733,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120250</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18008,6 +18843,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120251</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18132,6 +18972,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134684782</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18240,6 +19085,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134684770</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18348,6 +19198,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134684774</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18463,6 +19318,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80741416</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18574,6 +19434,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116259485</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18688,6 +19553,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134684778</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18799,6 +19669,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134684781</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18915,6 +19790,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772890</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19017,6 +19897,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772896</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19133,6 +20018,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772948</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19240,6 +20130,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772963</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19359,6 +20254,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772895</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19466,6 +20366,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772894</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19568,6 +20473,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772898</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19680,6 +20590,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772945</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19787,6 +20702,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772946</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19894,6 +20814,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772947</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20001,6 +20926,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772950</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20108,6 +21038,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772952</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20215,6 +21150,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772953</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20322,6 +21262,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772954</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20429,6 +21374,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772955</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20536,6 +21486,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772961</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20643,6 +21598,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772962</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20750,6 +21710,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772964</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20857,6 +21822,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116259075</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20954,6 +21924,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973998</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21059,6 +22034,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772705</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21160,6 +22140,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772722</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21257,6 +22242,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96964013</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21354,6 +22344,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974020</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21459,6 +22454,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120203</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21560,6 +22560,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104281159</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21666,6 +22671,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6625223</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21772,6 +22782,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6625224</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21874,6 +22889,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286339</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21976,6 +22996,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286362</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22078,6 +23103,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286367</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22180,6 +23210,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286369</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22277,6 +23312,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96963991</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22374,6 +23414,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974001</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22471,6 +23516,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974002</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22568,6 +23618,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974003</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22666,6 +23721,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112255</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22771,6 +23831,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120253</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22876,6 +23941,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120255</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22981,6 +24051,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120256</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23086,6 +24161,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120257</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23191,6 +24271,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120258</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23296,6 +24381,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120259</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23397,6 +24487,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179750</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23498,6 +24593,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104281160</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23599,6 +24699,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120280</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23701,6 +24806,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120204</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23803,6 +24913,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104281156</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23905,6 +25020,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286371</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24003,6 +25123,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112257</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24108,6 +25233,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120231</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24207,6 +25337,11 @@
       <c r="AY227" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725819</t>
         </is>
       </c>
     </row>
@@ -24314,6 +25449,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725866</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24415,6 +25555,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015019</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24512,6 +25657,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96964007</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24609,6 +25759,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96964008</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24706,6 +25861,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96964009</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24803,6 +25963,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974012</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24900,6 +26065,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974013</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24997,6 +26167,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96974014</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25105,6 +26280,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112847</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25207,6 +26387,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120272</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25309,6 +26494,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120274</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25409,6 +26599,11 @@
       <c r="AY239" t="inlineStr">
         <is>
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120276</t>
         </is>
       </c>
     </row>
@@ -25512,8 +26707,254 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120369935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>